--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -1849,7 +1849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4466,6 +4466,90 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DD-62</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>操作系统基线定为 Ubuntu Server 24.04 LTS + PostgreSQL 16；生产基线实施启动时另行冻结</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LD-08 原本没有写 OS 基线，是一处空白。而开发环境必须与生产同系，否则 Ansible 剧本与容器基础镜像要维护两套。候选为 Ubuntu 24.04 LTS（2024-04 发布，标准支持至 2029-04，ESM 至 2034）与 26.04 LTS（2026-04 发布，标准支持至 2031-04，ESM 至 2036）。</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>开发环境用 Ubuntu Server 24.04 LTS + PostgreSQL 16。四条理由按分量排：一、零返工——24.04 的默认仓库即 PG 16，正是设计文档所写、DDL 已验证通过的版本；二、不需要 PGDG 第三方源，离线镜像少一条供给链，无外网环境下每少一条链就少一个断供点；三、生态成熟两年半，组件的容器镜像与文档都按 24.04 写，遇到问题查得到；四、安全性不劣——Ubuntu 在标准支持期内对 LTS 回移安全补丁，24.04 与 26.04 拿到的维护同等，而 26.04 发布仅五个月，未被发现的问题更多。 生产版本基线在实施启动时另行冻结（LD-09 第 7 章），届时 26.04 已运行一年以上可重新评估；若定 26.04，开发环境按 Ansible 剧本重建一次即可。 配套纪律：剧本中 OS 版本与 PG 版本必须是 inventory 里的变量，不写死。</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>一、开发与生产均用 Ubuntu 26.04 LTS + PostgreSQL 18。二、改用 RHEL 系（Rocky Linux 9）。</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>一、需重新验证 DDL、PostGIS 与 Patroni 兼容性并改动 LD-02 与组件清单，换来的只是标准支持晚两年结束——而 24.04 与 26.04 都覆盖不了八年合同期，这是时点问题不是性质问题。二、Podman 与 Ansible 虽为 Red Hat 原生、MOI 环境亦可能为 RHEL 系，但生产 OS 由 MOI 与总包商决定，本方不宜单方面选定；该确认事项已提出，若答复为 RHEL 系则本决策推翻，越早发现代价越小。</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>中（开发环境可按剧本重建；生产基线尚未冻结，此时改动成本低）</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>REQ-LIC-08 · REQ-SEC-06 · LD-08 · LD-09 第 7 章 · CN-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DD-63</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>排序规则：集群默认 C，语言相关排序显式用 ICU 并声明在列上</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>数据库集群的排序规则若绑定 glibc（如 en_US.UTF-8），则 glibc 大版本升级时排序规则改变，已有文本索引【静默】失效——索引按旧规则排、查询按新规则找，查不到本该查到的行且不报错。而本项目八年合同期内必然发生一次 OS 大版本升级（Ubuntu 24.04 标准支持至 2029-04），即必然撞上这件事。同时阿拉伯语与英文的自然语言排序又确实需要语言学规则：实测 ICU ar 把 همزة 变体归到一起（أحمد 与 احمد 相邻），字节序则把同一名字的两种拼法拆到列表两端；ICU en 忽略大小写混排，字节序把全部大写排在小写之前。</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>集群默认 LC_COLLATE=C（字节序），与 OS 的 libc 解耦：glibc 升级不影响任何索引。 语言相关的排序显式使用 ICU，并声明在【列】上而非写在查询里：面向用户的阿拉伯语名称 COLLATE "ar-x-icu"，面向用户的英文名称 COLLATE "en-x-icu"。声明在列上的关键价值是 ORDER BY name_ar 自动使用该规则，不依赖每条查询都记得写 COLLATE——而漏写 COLLATE 不会报错，只是排序不对，阿语母语者一眼看得出、本方看不出。 编码、代码值、自然键，以及英阿混排的自由文本（不参与自然语言排序的）一律保持 C。 ICU 版本变化由 PostgreSQL 的 collation version 管理：pg_collation.collversion 与 pg_collation_actual_version() 不符时告警，按 infra/runbook 的检查脚本找出受影响的索引并 REINDEX。这比 glibc 的静默失效好在「它会告诉你」。</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>一、集群整体建在 glibc 的 en_US.UTF-8 上。二、集群整体使用 ICU 阿语排序（--locale-provider=icu --icu-locale=ar）。三、全部保持 C，不做语言学排序。</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>一、八年内必然发生的 OS 大版本升级会让全部文本索引静默失效，这是本设计不能接受的失败模式。二、可行但把全部文本索引都绑在 ICU 版本上，ICU 升级需全库 REINDEX；而实际需要语言学排序的只是少数面向用户的名称列，代价与收益不成比例。三、阿语与英文的排序会明显错误，且这类错误本方看不出来（见所选方案中的实测对比）。</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>低（集群 locale 在 initdb 时确定，事后更改需重建整个集群；列级 collation 可 ALTER，但已有索引需 REINDEX）</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>REQ-RPT-09 · DD-22 · LD-02 · LD-03 · LD-05 3.1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -628,6 +628,13 @@
       <c r="A26" t="inlineStr">
         <is>
           <t>【2026-09 补充】DD-53 至 DD-55 为详细设计第二轮讨论结论：旁路数据源经逐项核实后清空——排班改派生、勤务级别保留非必选接口、质检属 IRMS 不在范围。本系统因此不存在人工录入的业务数据源，M-10 仅维护参照数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】CN-37 补上资源表的一处漏项：CN-30 与 CN-31 都写明移动端经 DMZ 反向代理访问内网，但虚机资源表中从无这两台代理。该条同时固定三条范围边界——WAF 与证书由平台提供、移动应用管理不在本方范围、DMZ 不持有任何业务数据与凭据。IR-44 为移动端并发规模，决定代理对的规格是否够用。</t>
         </is>
       </c>
     </row>
@@ -642,7 +649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1834,6 +1841,38 @@
       <c r="F37" s="5" t="inlineStr">
         <is>
           <t>REQ-MIG-01 · REQ-MIG-05 · REQ-MIG-08 · REQ-ING-01 · AS-02 · IR-42 · DD-52</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>CN-37</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>DMZ 区内本方只交付接入代理；WAF、DDoS 防护、公网域名与证书由平台提供，移动应用管理不在本方范围</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>现场条件 + 商务范围</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>商务</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>细化 CN-30 与 CN-31 的划界，并补上一处漏项：两者都写明移动端经 DMZ 反向代理访问内网，但虚机资源表中从无这两台代理。后果有三：一、生产资源表增列 PROXY-1..2（各 4 vCPU、8 GB、100 GB 系统盘，无数据盘），生产由 22 台增至 24 台，合计由 27 台增至 29 台；二、DMZ 主机不持有任何业务数据与凭据库，凭据校验由内网 IAM 完成，代理仅转发，故 DMZ 被攻破的损失边界限于转发能力本身；三、新增 NW-04，规定代理只接受经平台 WAF 转发的入向流量、向内网仅在指定端口单向发起，内网不向 DMZ 发起连接。若平台不提供 WAF 与证书，或要求本方承担移动应用管理，虚机数量与交付范围须重新评估（T-33）。</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>REQ-MOB-01 · REQ-SEC-01 · REQ-SEC-06 · CN-30 · CN-31 · IR-44</t>
         </is>
       </c>
     </row>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -635,6 +635,13 @@
       <c r="A28" t="inlineStr">
         <is>
           <t>【2026-10 补充】CN-37 补上资源表的一处漏项：CN-30 与 CN-31 都写明移动端经 DMZ 反向代理访问内网，但虚机资源表中从无这两台代理。该条同时固定三条范围边界——WAF 与证书由平台提供、移动应用管理不在本方范围、DMZ 不持有任何业务数据与凭据。IR-44 为移动端并发规模，决定代理对的规格是否够用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-64 为研读 CloudICP 接口文档后新增：话务接入分话单与实时两条通道，考核类指标一律由本方从话单自算，平台 396 个 IDX 指标仅作对账基准与看板之用。CN-21 所说的「只能与话务平台自身报表比对」由此有了具体对象。</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4589,6 +4596,48 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DD-64</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>话务接入分两条通道；考核类话务指标一律由本方从话单自算，平台 IDX 指标仅用于对账与看板</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CloudICP 的 CMS 接口同时提供原始话单（CSV 下载）与 396 个平台指标编号（hindex / rindex）。同一个话务指标两边都能出，数值必然不一致。若不事先单选权威来源，报表与对账会各执一词。另一方面，hindex 的前置条件是「报表脚本已执行、话单已导入数据库」，rindex 与 real 则无此要求——历史指标与实时指标不是两种精度，是两种性质。</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>一、话单通道（reports/vdnvoicecalldetail）取原始话单，承载全部进入考核与封账的指标；二、实时通道（rindex / real）只供墙面大屏与实时看板，不进入封账、不作服务水平举证；三、平台 IDX 指标选定一组作为对账基准，差异按 LD-01 8.4 处置。</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>一、直接采用平台 IDX 指标作为考核口径，本方不自算。二、两套都入库，报表按场景择一。</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>一、平台指标不可回溯到明细行：客户问「这个数是哪些电话算出来的」时答不了，而指标口径唯一的前提是口径可以被打开看；且其新鲜度依赖 ICP 的报表批，而服务等级按日考核，举证材料的产生时刻不能挂在另一方的批处理上。二、两套并存即两套口径，与本设计「口径唯一」的立场直接冲突，且差异会在客户面前以「同一个指标两个数」的形式出现。</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>中（通道划分与口径来源改变会波及 LD-03 的话务指标定义与 LD-05 的实时档，但不涉及库结构重建）</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>REQ-ING-03 · REQ-RPT-06 · REQ-PRF-01 · CN-21 · AS-30 · AS-31 · IR-45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -642,6 +642,13 @@
       <c r="A30" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-64 为研读 CloudICP 接口文档后新增：话务接入分话单与实时两条通道，考核类指标一律由本方从话单自算，平台 396 个 IDX 指标仅作对账基准与看板之用。CN-21 所说的「只能与话务平台自身报表比对」由此有了具体对象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-65 为 DD-64 的例外：坐席状态时长一类事实在话单中不存在，以平台历史指标为唯一来源并在报表标注、不可下钻。同轮完成了 396 个平台指标与本方话务指标的逐条对照，结论记于 metrics/icp_source_map.yaml；M-C09 至 M-C13 与 M-C15 六条随 IR-11 答复解除依赖并发布。</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4638,6 +4645,48 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DD-65</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>无明细源的话务指标以平台历史指标为唯一来源，并在报表上标注来源且不可下钻（DD-64 的例外）</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DD-64 规定考核类话务指标一律由本方从话单自算。但话单只记呼叫，不记坐席的签入签出与状态变化——在岗时长、各状态时长、占用率这一类事实在话单里根本不存在。若机械执行 DD-64，这些指标将无法交付，而 RFP 1.6.2.25 要求坐席状态时长分解（R-26）。</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>此类指标以平台历史指标为唯一来源：M-R01 取 IDX_04_03_001 签入签出统计，M-R02 取 IDX_04_02_002 签入时长，M-R03 取 IDX_04_02_* 各状态时长，M-R04 由应答时长与事后处理时长除以签入时长得出。相应报表须标注数据来源为话务平台，并明确不可下钻到单次状态变化——它们是日累计值。逐条对应关系记于 metrics/icp_source_map.yaml。</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>一、由本方按轮询实时接口采样自行累计状态时长。二、放弃该类指标，向 MOI 说明不可交付。</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>一、采样累计的精度被轮询周期锁死，且两次采样之间的状态变化不可见；更要紧的是它会产生一个与平台自身报表必然不一致的数，而我方拿不出更可信的底稿——这正是 CN-21 指出的处境。既然精度不占优，不如直接用平台口径并如实标注来源。二、RFP 1.6.2.25 有明文要求，不可交付即不合规。</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>低（来源切换只影响接入与指标计算，不涉及库结构；若日后 ICP 开放状态流水，可改为自算并递增指标版本）</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>REQ-RPT-06 · REQ-ING-03 · DD-64 · CN-21 · IR-45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -649,6 +649,13 @@
       <c r="A32" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-65 为 DD-64 的例外：坐席状态时长一类事实在话单中不存在，以平台历史指标为唯一来源并在报表标注、不可下钻。同轮完成了 396 个平台指标与本方话务指标的逐条对照，结论记于 metrics/icp_source_map.yaml；M-C09 至 M-C13 与 M-C15 六条随 IR-11 答复解除依赖并发布。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-66 把话务事实拆为腿级与通话级两张表，通话级由腿级聚合构建。同轮按 DD-65 把坐席状态时长改为平台日累计（core.fact_agent_day），而签入签出区间仍为明细（core.fact_agent_session），DD-53 的班次求交口径不受影响。DD-65 的条文已就此更正：当时误把签入签出一并列入例外。</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4179,7 +4186,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>REQ-DSH-04 · DD-41 · M-10 · R-22</t>
+          <t>REQ-DSH-04 · DD-41 · M-10 · R-22 · DD-65 · DD-66（本条正文中的 fact_agent_state 已按 DD-66 拆为 fact_agent_session 与 fact_agent_day，班次求交改用前者；按维护规则正文保留原状）</t>
         </is>
       </c>
     </row>
@@ -4658,12 +4665,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DD-64 规定考核类话务指标一律由本方从话单自算。但话单只记呼叫，不记坐席的签入签出与状态变化——在岗时长、各状态时长、占用率这一类事实在话单里根本不存在。若机械执行 DD-64，这些指标将无法交付，而 RFP 1.6.2.25 要求坐席状态时长分解（R-26）。</t>
+          <t>DD-64 规定考核类话务指标一律由本方从话单自算。但话单只记呼叫，不记坐席的状态变化——各状态时长与占用率这一类事实在明细中不存在：平台只给到日累计，「这名坐席 10 点 05 分从通话转为事后处理」在任何接口里都查不到。若机械执行 DD-64，这些指标将无法交付，而 RFP 1.6.2.25 要求坐席状态时长分解（R-26）。需要分清的是签入签出：IDX_04_03_001 返回的是 {inTime, outTime, duration} 区间数组，那是明细，不在本例外之列。</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>此类指标以平台历史指标为唯一来源：M-R01 取 IDX_04_03_001 签入签出统计，M-R02 取 IDX_04_02_002 签入时长，M-R03 取 IDX_04_02_* 各状态时长，M-R04 由应答时长与事后处理时长除以签入时长得出。相应报表须标注数据来源为话务平台，并明确不可下钻到单次状态变化——它们是日累计值。逐条对应关系记于 metrics/icp_source_map.yaml。</t>
+          <t>状态时长类指标以平台历史指标为唯一来源：M-R03 取 IDX_04_02_* 各状态时长，M-R04 由应答时长与事后处理时长除以签入时长得出。相应报表须标注数据来源为话务平台，并明确不可下钻到单次状态变化，也不可按班次切分——平台只给到坐席日粒度。签入签出区间落入 core.fact_agent_session 照常自算，M-R01 与 M-R02 可按班次窗口求交，DD-53 不受影响。逐条对应关系记于 metrics/icp_source_map.yaml。</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4683,7 +4690,49 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>REQ-RPT-06 · REQ-ING-03 · DD-64 · CN-21 · IR-45</t>
+          <t>REQ-RPT-06 · REQ-ING-03 · DD-53 · DD-64 · CN-21 · IR-45</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DD-66</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>话务拆为腿级与通话级两张事实表；通话级由腿级聚合构建，不独立接入</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ICP 话单的粒度是「呼叫每经过一个设备一行」而非一通一行（LD-01 4.3）。原 core.fact_call 按一通一行设计，与源端对不上：等待时长在排队腿上、通话时长在坐席腿上、转接表现为同一 CALLID 下出现第二个坐席腿。若只建通话级表，这些事实在接入时就被压扁，按坐席的指标（M-C09 至 M-C13）无从计算，口径分歧也失去可回溯的底稿。</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>core.fact_call_leg 与话单一行一一对应，幂等键为 CALLID + CALLIDNUM，是唯一的接入落点；core.fact_call 为通话级，由腿级聚合构建，每一列都必须能从腿级重算。按坐席的指标一律从腿级算，通话级只服务于通话粒度的报表与快速归属。随之新增 agent_leg_count 与 answered_leg_count 两列，使「呈现」与「接通」在通话级可直接区分。</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>一、只建通话级表，腿级信息在接入时压扁。二、只建腿级表，通话级用视图或 mart 层聚合。</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>一、压扁即不可逆，等待与通话的归属、转接的判定全部在接入侧写死，此后任何口径分歧都无底稿可查，与 raw 层不做解释（DD-58）的立场也不一致。二、通话级被 bridge_call_intake 与多张报表直接引用，全部改走视图会把聚合成本摊到每次查询上；且通话级与接警单的关联是多对多，物化一张表更利于行级过滤的下推。</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>高（粒度变更涉及事实表结构、模型构建与全部话务指标的计算式；但当前尚未部署，此时改动代价最低）</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>REQ-ING-03 · REQ-RPT-06 · DD-58 · DD-64 · AS-31 · IR-11</t>
         </is>
       </c>
     </row>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,13 @@
       <c r="A34" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-66 把话务事实拆为腿级与通话级两张表，通话级由腿级聚合构建。同轮按 DD-65 把坐席状态时长改为平台日累计（core.fact_agent_day），而签入签出区间仍为明细（core.fact_agent_session），DD-53 的班次求交口径不受影响。DD-65 的条文已就此更正：当时误把签入签出一并列入例外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-67 定下连接层拓扑：pgBouncer 在前、HAProxy 在后（选主由 Patroni 的健康检查承担），两个池按事务级与会话级分工，LB 对走 active/passive，生产 max_connections 提至 200。开发环境第 5 步已按此落地并实测通过。</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4736,6 +4743,48 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DD-67</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>连接层拓扑：应用 → pgBouncer → HAProxy → 当前主库；两个池；LB 对按 active/passive；生产 max_connections 提至 200</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>pgBouncer 自身没有选主能力，其 [databases] 段只能写一个固定地址；知道谁是主库的是 Patroni。若把 HAProxy 放在 pgBouncer 之前，每个 pgBouncer 只能绑死一台库，池就跟着库走，备库上的池常态闲置，集中控制连接数的目的落空。另一方面，事务级池化省连接，但 SET、临时表、advisory lock 与预处理语句不保证落在同一后端连接上，而 Airflow 与 dbt 都依赖这些。</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>一、顺序定为 应用 → pgBouncer → HAProxy → 当前主库。pgBouncer 的后端固定为本机 HAProxy；HAProxy 以 Patroni 的 REST /primary 作健康检查选主。二、两个池：业务查询走事务级，Airflow / dbt / 人工运维走会话级；会话池大小即 dbt 并发上限，两数绑定。三、LB 对按 active/passive（VIP 浮动）部署。四、生产 max_connections 由 100 提至 200，为切换瞬间的池叠加与临时人工连接留出名额。</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>一、HAProxy 在前、pgBouncer 在后。二、只用一个事务级池。三、LB 对按 active/active 部署。</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>一、见上：池跟着库走，且备库池闲置。二、dbt 与 Airflow 会在运行期随机失败——事务级池化下临时表与会话变量不是必然失效，而是偶尔失效，这类缺陷在生产高负载时才显形，排查成本极高。三、AA 若靠 DNS 轮询实现，DNS 缓存会让故障节点继续收流量，切换反而比 AP 慢；要做对需在前面再加一层四层负载均衡，离网环境中即多一条供给链。AA 常态下两份池同时活着，后端连接翻倍，且主库切换时有两套陈旧连接各自清理。本项目并发量不高，少一个活动部件就少一类事故——按日考核 0.86 秒的容差本就不可能靠「切得快」达标，只能靠「不出事」。</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>中（拓扑与池模式改变会波及连接串与 ETL 行为，但不涉及库结构；max_connections 为重启参数）</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>REQ-PRF-01 · REQ-AVL-01 · REQ-OPS-01 · DD-11 · DD-43 · RS-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -663,6 +663,13 @@
       <c r="A36" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-67 定下连接层拓扑：pgBouncer 在前、HAProxy 在后（选主由 Patroni 的健康检查承担），两个池按事务级与会话级分工，LB 对走 active/passive，生产 max_connections 提至 200。开发环境第 5 步已按此落地并实测通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-68 补上一处空白：此前只有静态加密（T-15），没有传输加密。生产的库连接跨虚机，而开发机上三者同机、回环不出网卡，这一项在开发环境里永远验不到——正因如此更容易被漏掉。LD-07 新增第 7 章，LD-08 第 9 章新增 NW-06（二十条→二十一条）。</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4785,6 +4792,48 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DD-68</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>跨虚机的数据库连接与复制流量启用 TLS，客户端取 sslmode = verify-full，证书由 MOI 内部 CA 签发</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>生产拓扑中 pgBouncer 与 HAProxy 在 LB 节点、PostgreSQL 在库虚机（DD-67），库连接因此跨虚机走一段真实的内网链路，链路上是全部警情明细、报警人号码与位置坐标。此前设计只覆盖了静态加密（T-15），传输加密是一处空白——而开发机上三者同机、回环不出网卡，这一项在开发环境里永远验不到，正因如此更容易被漏掉。</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>库连接与复制流量一律启用 TLS，客户端侧取 sslmode = verify-full；证书由 MOI 既有的内部 CA（AD CS）签发，本方不自建 CA、不使用自签证书。吊销点须在内网可达，并给出证书轮换周期与通知方式——列为对基础设施提供方的要求 NW-06。轮换规程与演练并入 LD-08 的演练规程，与切换演练同等对待。</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>一、sslmode = require。二、不加密，以「内网已分段」为由。三、本方自建 CA 或使用自签证书。</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>一、require 只加密不验证对端身份，中间人仍可冒充库端完成握手；它挡住的是被动监听，挡不住主动劫持，而在一个已分段的内网里值得防的恰恰是后者。二、分段降低的是暴露面而不是链路本身的机密性；且按日考核的举证要求下，「当时链路是明文的」在事后无法补救。三、自签证书要么逼着客户端关校验，要么要在每台机器上单独布信任，两者都会在扩容时失守；而现场已有 AD CS，自建 CA 是在既有能力之外另造一套。</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>中（启用 TLS 涉及证书签发与分发流程，但不改库结构与应用逻辑；sslmode 为连接串参数）</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>REQ-SEC-01 · REQ-SEC-06 · DD-67 · T-15 · NW-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -670,6 +670,13 @@
       <c r="A38" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-68 补上一处空白：此前只有静态加密（T-15），没有传输加密。生产的库连接跨虚机，而开发机上三者同机、回环不出网卡，这一项在开发环境里永远验不到——正因如此更容易被漏掉。LD-07 新增第 7 章，LD-08 第 9 章新增 NW-06（二十条→二十一条）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-69 记录 Python 依赖的两级冻结方式：Airflow 取上游官方 constraints（SHA-256 入 MANIFEST），dbt 由本方自维护 lock；两者统一离线安装。同轮修正了一处只在有网环境才看不出的缺陷——取料用的 pip download 虽不重复下载字节，却仍每次连 PyPI 重新解析依赖，剧本因此在真正离网的机器上跑不起来；现取料由 wheelhouse_refresh 开关控制，默认关闭。</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4834,6 +4841,48 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DD-69</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Python 依赖采用两级冻结：Airflow 用上游官方 constraints，dbt 用本方自维护的 lock；两者都离线安装，不在装机时解析依赖</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Airflow 的依赖树有数百个包，上游为每个版本发布经过 CI 验证的 constraints 文件；dbt 没有同类文件。若两者都放任 pip 在装机时自行解析，同一份剧本在不同时间装出的环境不同，且解析本身需要联网——而生产网离网。</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>一、Airflow 侧固定取 constraints-{版本}/constraints-{python 版本}.txt，其 SHA-256 记入 infra/artifacts/MANIFEST.md，与 ISO、OS 包、容器镜像同一套溯源纪律。二、dbt 侧由本方在有网环境解析一次，pip freeze 冻结为 infra/dbt-requirements.lock 并入库，升级 dbt 时重新解析并复核。三、两者统一经 pip download 取料到 wheelhouse，安装时 --no-index --find-links，装机过程不联网。四、取料阶段由 wheelhouse_refresh 开关控制，默认关闭。</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>一、装机时直接 pip install，用 requirements.txt 约定版本范围。二、dbt 也套用 Airflow 的 constraints 文件。三、把 wheelhouse 作为剧本每次运行都重新取料的产物。</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>一、版本范围不是冻结，传递依赖仍会漂；且离网装不了。二、Airflow 的 constraints 是为 Airflow 的依赖树验证的，把 dbt 及其适配器压进同一组约束会产生上游从未验证过的组合，冲突时无人可追。三、取料需要联网，剧本会在真正离网的机器上跑不起来——这正是开发机有网掩盖掉的问题；字节虽然不会重复下载，但 pip 仍会每次连 PyPI 重新解析。</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>低（依赖冻结方式可随时调整，不涉及库结构与应用逻辑；但 dbt lock 的维护责任由本方承担，是一项长期运维义务）</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>REQ-OPS-01 · REQ-OPS-04 · CN-19 · DD-47 · DD-49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -677,6 +677,13 @@
       <c r="A40" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-69 记录 Python 依赖的两级冻结方式：Airflow 取上游官方 constraints（SHA-256 入 MANIFEST），dbt 由本方自维护 lock；两者统一离线安装。同轮修正了一处只在有网环境才看不出的缺陷——取料用的 pip download 虽不重复下载字节，却仍每次连 PyPI 重新解析依赖，剧本因此在真正离网的机器上跑不起来；现取料由 wheelhouse_refresh 开关控制，默认关闭。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-70 与 DD-71 定下发布形态：权威来源是 Ansible 剧本而非虚机镜像，离网介质自带 apt / PyPI / 容器三个仓库，构建期依赖不进墙内（npm 这条供给链在生产网内因此不存在）。两条都来自 2026-10-08 在开发机上对交付路径的实测，而实测推翻了两处原本写进规程的做法：pip download 会把只发源码包的依赖原样带进墙内（改用 pip wheel），podman save/load 不保 digest 以致 load 直接拒绝（改用 skopeo + OCI 目录）。通用教训：交付路径上的每一个工具，都要在还有退路的时候实际跑一遍——开发机能上网这件事，会把离网问题推迟到最糟的时刻才暴露。IR-47（虚机基线）与 IR-48（介质导入流程与扫描网关是否改写文件）在答复前，介质的组织方式不能定稿。</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4883,6 +4890,90 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DD-70</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>发布形态：Ansible 剧本为权威来源，虚机镜像只能是剧本的派生产物；离网介质自带 apt / PyPI / 容器三个仓库；构建期依赖不进墙内</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MOI 生产网离网，且内网没有 apt 镜像、PyPI 镜像与容器镜像仓库。交付形态有两种候选：发一个装好的虚机镜像，还是发一套可执行的装配说明（剧本 + 物料）。八年合同期内还要持续打补丁。</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>一、权威来源是 infra/ 目录（剧本 + inventory + MANIFEST），镜像若出也必须由剧本跑出来，且纪律为「镜像里不许有剧本装不出来的东西」。二、介质自带三个仓库：签名的本地 apt 仓库（只含依赖闭包，非整源镜像）、wheelhouse（只含轮子）、OCI 目录（容器镜像）。三、区分构建期与运行期依赖，只有运行期依赖跨墙——门户前端的 Node/TypeScript 工具链不进生产网，只带编译产物 dist/，npm 这条供给链在墙内因此不存在。四、介质由剧本生成（90-bundle.yml），不手工攒。五、验收须在网卡真正禁用的全新虚机上、由另一个人重做一遍。做法记于 runbook/90-offline-media.md。</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>一、以虚机镜像为交付物（权威）。二、要求 MOI 在内网建三个仓库。三、把前端构建工具链一并带进生产网。</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>一、三条独立理由：①镜像把 OS 冻在打镜像那一刻，八年里每轮补丁要么让镜像作废要么要重走 MOI 审批（CN-13、CN-14）；②平台方若按自家基线交付虚机（IR-47），绕过其加固与补丁通道的自制镜像过不了安全审计；③分发镜像等于分发整个 Ubuntu 的 GPL 二进制，我方由此成为分发者并产生「提供对应源码」的持续义务（GPLv2 §3 / v3 §6）及修改版镜像的商标与再分发问题——而交付剧本与校验和则什么都没分发。二、不在我方可控范围，且把交付时点押在客户的基础设施建设上。三、带进墙内的每一样东西都是八年的维护义务；且构建失败的现场排查成本极高。</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>中（权威来源形态的改变会波及整个交付包的组织方式，但不涉及库结构与应用逻辑；镜像作为派生产物可随时增减）</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>REQ-OPS-01 · REQ-OPS-04 · CN-19 · DD-49 · DD-69 · IR-47 · IR-48</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DD-71</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>容器镜像跨墙用 skopeo + OCI 目录传递，复验锚点落在介质上的 manifest 而非本机镜像库</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>镜像要随介质跨墙，而墙内没有镜像仓库。MANIFEST 以 digest 钉死镜像（DD-46 一线的纪律），但 digest 能否完整穿过介质此前从未实测。</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>一、用 skopeo copy --all 从仓库拷到介质上的 OCI 目录（manifest 逐字节拷贝，多架构 manifest list 一并带走）。二、现场复验用 skopeo inspect --raw &lt;OCI 目录&gt; | sha256sum，结果应等于 MANIFEST 记录的 digest——digest 的定义即 manifest 自身的 SHA-256，故该复验离网可做、不需要仓库、不信任任何中间环节。三、导入本机库时不得带 --all（containers-storage 存不下一组镜像），须以 --override-os/--override-arch 指定平台。四、skopeo 进 apt 闭包与 MANIFEST，墙内也要装。</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>一、podman save / podman load。二、不校验 digest，只校验归档文件的 SHA-256。</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>一、2026-10-08 在开发机实测：save --format oci-archive 之后 load 直接拒绝（Digest of source image's manifest would not match destination reference）。原因是上游 tag 为多架构 manifest list，而 save 只导出当前平台那一份，list 丢失后归档内容算出的 digest 与归档中记录的引用名不符。这不是配置问题，是该路径本身不保 digest。二、归档文件的哈希只能证明文件没在复制中损坏，证明不了它就是上游发布的那个镜像——与 ISO 校验必须先验签名再比哈希（MANIFEST「ISO 的校验方式」）是同一个道理。</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>低（传递工具与复验命令可更换，不影响镜像内容与运行形态；但复验锚点一旦改变须同步改写 MANIFEST 的纪律条文）</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>REQ-OPS-01 · CN-19 · DD-46 · DD-70 · T-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -684,6 +684,13 @@
       <c r="A42" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-70 与 DD-71 定下发布形态：权威来源是 Ansible 剧本而非虚机镜像，离网介质自带 apt / PyPI / 容器三个仓库，构建期依赖不进墙内（npm 这条供给链在生产网内因此不存在）。两条都来自 2026-10-08 在开发机上对交付路径的实测，而实测推翻了两处原本写进规程的做法：pip download 会把只发源码包的依赖原样带进墙内（改用 pip wheel），podman save/load 不保 digest 以致 load 直接拒绝（改用 skopeo + OCI 目录）。通用教训：交付路径上的每一个工具，都要在还有退路的时候实际跑一遍——开发机能上网这件事，会把离网问题推迟到最糟的时刻才暴露。IR-47（虚机基线）与 IR-48（介质导入流程与扫描网关是否改写文件）在答复前，介质的组织方式不能定稿。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-72 改写了 LD-07 第 6 章的身份方案：由「Keycloak 以 LDAP 直连 AD」改为「经 AD FS 做身份代理」。这不是实现细节的调整——前一种写法会让用户的域口令经过我方登录页，并把 MOI 的 MFA 与条件访问策略整体绕过。第 6 章随之重写为 6.1–6.7，新增两项此前完全缺失的内容：令牌签名证书自动轮换会在某一天使全部登录同时失败（故上游 IdP 必须按元数据 URL 刷新，元数据 URL 要进网络策略，与第 7 章要求 CRL/OCSP 可达同类），以及标识同一个人的声明必须是不可变标识，否则人员改名调岗后授权与审计关联会断开。IR-39 改写为「部门组能否作为声明传出」（AD 里有这个组与这个组能出现在令牌里是两件事），IR-49 为 AD FS 的对接规格与测试账号。</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4974,6 +4981,48 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DD-72</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>身份经 AD FS 做身份代理（identity brokering），不让 Keycloak 直连 AD DS 做 LDAP 联邦</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MOI 已部署完整微软身份栈（AD DS / AD FS / AD CS）。Keycloak 有两种对接方式：User Federation 以 LDAP 直连域控，用户在我方登录页输入域口令；Identity Brokering 把登录重定向到 AD FS，我方只校验 AD FS 签发的令牌。此前 LD-07 第 6 章写的是前者。</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>取 Identity Brokering。协议优先 OIDC，AD FS 若只开放 SAML 2.0 或 WS-Fed 则按实际开放的协议定稿（IR-49）。服务层只认 Keycloak 签发的令牌，不直接校验 AD FS 的令牌，使受众划分、角色映射与有效期策略有统一落点。人的身份走该链路，机器身份（esb / ai_pkg / mcp）用 Keycloak 自身的 OAuth2 客户端凭证，与 AD 无关。上游 IdP 按元数据 URL 定期刷新而非粘贴静态证书。标识「同一个人」的声明须为不可变标识（objectGUID 一类），不得用 sAMAccountName 或 UPN。</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>一、Keycloak User Federation，以 LDAP 直连 MGMTADDS01/02。二、本系统自建用户目录，由 MOI 批量导入并定期同步。</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>一、四条独立理由：①用户的域口令会经过我方登录页与进程内存，是任何一次安全审查都要重点解释的事；②MOI 的 MFA、设备合规、登录位置限制等条件访问策略作用在 AD FS 的认证环节，LDAP bind 会把它们全部绕过，而「绕过」通常到审计时才被发现；③锁定阈值、过期提醒、首次登录改密、禁用账号即时生效等口令策略语义要我方逐条复刻，复刻不对即成安全缺口；④要长期保管一个有目录读权限的绑定账号，泄露时影响整个目录而非只本系统。二、复制用户数据即产生两份权威与同步时延，禁用账号无法即时生效，且与 RFP 的单一身份要求相悖。</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>中（对接方式的改变涉及 Keycloak 配置与 AD FS 侧的信赖方配置，但不改库结构与应用逻辑；代价是多一跳依赖与一项证书轮换的长期运维义务）</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>REQ-SEC-01 · REQ-SEC-02 · CN-30 · CN-31 · DD-68 · IR-39 · IR-49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -547,6 +547,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -624,6 +625,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -631,6 +633,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -638,6 +641,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -645,6 +649,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -652,6 +657,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -659,6 +665,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -666,6 +673,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -673,6 +681,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -680,6 +689,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -687,10 +697,19 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-72 改写了 LD-07 第 6 章的身份方案：由「Keycloak 以 LDAP 直连 AD」改为「经 AD FS 做身份代理」。这不是实现细节的调整——前一种写法会让用户的域口令经过我方登录页，并把 MOI 的 MFA 与条件访问策略整体绕过。第 6 章随之重写为 6.1–6.7，新增两项此前完全缺失的内容：令牌签名证书自动轮换会在某一天使全部登录同时失败（故上游 IdP 必须按元数据 URL 刷新，元数据 URL 要进网络策略，与第 7 章要求 CRL/OCSP 可达同类），以及标识同一个人的声明必须是不可变标识，否则人员改名调岗后授权与审计关联会断开。IR-39 改写为「部门组能否作为声明传出」（AD 里有这个组与这个组能出现在令牌里是两件事），IR-49 为 AD FS 的对接规格与测试账号。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-73 至 DD-76 来自第 1 批开发（DDL 落库）。开发机先在临时实例上试建，发现 SQL 本身无误，但缺三样东西：重复执行与版本登记的机制、属主与授权、以及一处 LD-06 与 DDL 的结构矛盾。DD-73 用词定为「结构变更」而非「迁移」，因本项目中「迁移」专指归档数据迁入；并记下一个名字陷阱——meta.schema_version_registry 记的是归档数据源的多版本，不是我方 DDL 版本。DD-74 让 raw 只追加（DD-02）由数据库授权执行而不只靠约定。DD-75 修正 LD-06 2.2：热调记录在结构上写不进 meta.run_log。DD-76 补上 LD-01 7.2 隔离区在 DDL 中缺失的表，并定为「登记」而非「搬移」。</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5023,6 +5042,174 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DD-73</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>数据库结构的执行与版本登记：按编号的「结构变更」逐个执行，幂等性来自「是否已执行」而非「对象是否存在」；已执行变更的文件不得再改</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ddl/01..05 共 1242 行从未真正执行过，且不能重跑（第二遍即报对象已存在），而剧本纪律要求第二遍 changed=0。LD-08 只写了「DDL 变更随制品发布，必须可前滚可回退」，没有定执行机制与版本记录。HD-04 中原无相关决策。2026-10-08 在开发机临时实例上试建：五个文件零报错，50 张表与 55 条索引全部建出，且可作为单个事务执行，失败时整体回滚。</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>一、用词定为「结构变更」（DDL change），不叫「迁移」——本项目中「迁移」专指 Hexagon 归档数据迁入（CN-15 · CN-16 · REQ-MIG-* · DD-37 · DD-57 至 DD-60），沿用行业惯例的 migration 会在交接检索时混成两类毫不相干的东西。二、清单 ddl/changes.yml 记「编号 → 文件列表」；ddl/01..05 原样作为变更 0001（LD-02 按文件名引用它们，不挪不改名）；此后的变更放 ddl/changes/。三、登记表 meta.ddl_change（变更 0000），一个变更一行，记文件列表与拼接后的 SHA-256；与 meta.release_registry（DD-49，一次发布一行）并列，一对多。四、每个变更的全部文件连同登记行在同一个事务中执行。五、已执行变更的文件校验和一旦变了，执行器必须失败并报出新旧校验和——结构只能新增变更来改，与登记册「不改写、只新增」同一条规矩。回退亦以新增一个反向变更实现，不撤销已执行的变更。六、执行器为 Ansible + psql，不另写工具。七、0000 至 0002 以超级用户执行（0001 建扩展，0002 建角色）；0003 起事务开头 SET LOCAL ROLE oss911_owner，新对象归属主。</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>一、给 CREATE TABLE / CREATE INDEX 加 IF NOT EXISTS。二、把变更记录写进 meta.release_registry。三、借用 meta.schema_version_registry 记录我方 DDL 版本。四、另写一个 Python 迁移工具（或引入 Flyway / Alembic 一类）。</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>一、表已存在但定义变了时 IF NOT EXISTS 会静默跳过：第二遍 changed=0，库里仍是旧结构且不报错——正是本项目最警惕的「安静地错」。例外：CREATE SCHEMA / CREATE EXTENSION IF NOT EXISTS 与 CREATE OR REPLACE FUNCTION 可保留，它们要么没有「定义」可言，要么真的会替换；ddl/01 中全是这一类。二、两者粒度不同：一次发布可含多个变更，也可一个都没有（只改了 dbt 模型或指标）。三、名字陷阱：该表记的是归档数据源在时间轴上的多版本结构（RFP 2.7.7.9 · DD-37，source_id + version_no，如「2016 年那套表结构与 2019 年不同」），与我方 DDL 版本是两件事；因名字相近，混用可能数月后才被发现。四、Ansible 与 psql 已在生产链上，多一个工具就多一份要送进离网环境、要维护八年的依赖（DD-70）。</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>中（执行机制可替换，但「已执行变更不可改」一旦被违反，各环境的实际结构即与仓库失同步，且难以发现）</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>REQ-OPS-01 · REQ-DB-01 · DD-02 · DD-49 · DD-70 · DD-74</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DD-74</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>数据库角色：五个不可登录的权限角色，按层分属主；分层写权限由数据库授权执行，而不只靠约定</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1242 行 DDL 中没有一行 OWNER、GRANT 或 CREATE ROLE；dbt profile 引用的 DBT_USER 在库中不存在，也没有任何剧本建过它。若以 postgres 建全部对象，所有对象属主均为超级用户，此后再改代价很大。LD-07 / LD-04 只规定了「不给服务账号开自由 SQL」（DD-51），没有写 schema 归谁、谁能写哪一层。</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>一、五个 NOLOGIN 权限角色：oss911_owner 持有 raw · core · meta · audit 全部对象与七个 schema；oss911_ingest 对 raw 只有 SELECT 与 INSERT，并写 meta 中的水位、运行日志、值剖析与映射登记；oss911_transform（dbt）对 raw 只读，对 core 可增删改但不能 DROP，staging · mart · ai 由它在运行时建并归它所有；oss911_query_svc 读 core · mart · ai · meta，对 audit 只 INSERT 访问与投递留痕；oss911_admin_svc 继承 query_svc，另写权限矩阵与参照配置表及其变更留痕，可查 audit（M-07）。二、可登录用户与口令按环境由剧本建立并加入相应角色；变更 0002 随发布制品进入生产，不得含口令或环境相关的用户名。三、ALTER DEFAULT PRIVILEGES 只管授权、不管属主——它保证新对象自动授权给其他角色，但不改变属主是谁。四、meta.ensure_daily_partitions 改为 SECURITY DEFINER（search_path 钉死），收窄到 core 与 audit 的分区表，EXECUTE 只授 oss911_transform：建分区要求调用者是父表属主，而编排调用时不是。五、写权限只授有依据的；依据不明者本次不授，代码写到时以新增变更补，并在提交说明里写明依据。由此产生三条硬约束：dbt profile 必须设 role: oss911_transform；core 模型只能以增量写入既有表（dbt 不是属主，--full-refresh 会失败，这是期望的行为）；raw 表必须由结构变更建，接入程序不得自建（属主天然拥有 DELETE 与 TRUNCATE）。新角色不需要改 pgbouncer 的 userlist.txt，其余用户经 auth_query 现查。</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>一、接入与 dbt 共用一个写入角色。二、服务层只设一个角色。三、dbt 以 SET ROLE oss911_owner 运行，使全部对象归属主。四、以超级用户建全部对象，不设属主角色。</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>一、那样 raw 只追加（DD-02）只靠约定维持；拆开后由权限执行纪律，而不靠人记得。二、管理界面经服务层写权限矩阵与参照配置（LD-06 2.1），若与查询路径同一角色，调用量最大、暴露面最大的查询路径一旦被打穿，即可改写字段可见性矩阵。三、那样 dbt 拥有属主的全部权力，包括删改 raw，DD-02 又退回靠约定。四、超级用户绕过一切授权检查，任何以它运行的程序都能删改 raw 与 audit；属主事后再改需逐对象 ALTER，且极易遗漏。</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>中（角色划分可增补，但属主一旦散落到登录用户上，事后收拢需逐对象处理；当前尚未落入开发库，此时定下代价最低）</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>REQ-SEC-01 · REQ-SEC-02 · DD-02 · DD-03 · DD-17 · DD-51 · DD-67 · DD-73</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DD-75</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>运行参数的热调留痕另设 audit.runtime_param_change_log，不写入 meta.run_log</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LD-06 2.2 写的是「运行参数的热调写 meta.run_log 的关联记录」。但 meta.run_log 是接入运行的记录，source_id、contract_version、outcome 均为必填，且 outcome 只允许 success / failed / quarantined / partial 四个接入结果——热调记录在结构上写不进去。开发机落库角色授权时发现此处无法授权（2026-10-11）。</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>新建 audit.runtime_param_change_log，与 audit.reference_data_change_log、audit.permission_change_log 并列：只增不改，逐字段记「改了哪个参数、旧值、新值、谁、何时、理由」。写入身份为 oss911_admin_svc。LD-06 2.2 的表述随之更正。三张留痕表结构不同但字段语义一致，查询时合并为一条时间线——这是 LD-06 2.2 原本就写下的意图。</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>一、放宽 meta.run_log 的必填约束与 outcome 取值，让热调记录也写进去。二、热调不留痕。</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>一、run_log 是接入血缘与水位推进的依据，混入另一类记录后，所有按 run_log 统计接入成败与时延的查询都要先过滤，漏过滤即算错；且放宽必填约束会同时放松对接入记录本身的约束。二、热调会改变速率与资源占用，事后排查「为什么那天慢了」时没有记录可查（LD-08 7.2 热调与发布的界线）。</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>低（新增一张留痕表，不改既有结构）</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>REQ-GOV-05 · REQ-OPS-01 · DD-74</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DD-76</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>隔离区以「登记」实现，不以「搬移」实现：坏批次照常落入 raw，另在 meta.quarantine_batch 登记状态，staging 只读未隔离或已放行的批次</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LD-01 7.2 设计了隔离区（批次原样保留、附失败原因，M-03 可查看、放行或丢弃，两者留审计），但 DDL 中没有对应的表。开发机落库授权时发现（2026-10-11）。</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>一、未通过校验的批次照常写入 raw。二、meta.quarantine_batch 一批一行：批次标识、运行标识、来源、失败原因、状态（待处理 · 已放行 · 已丢弃）、处理人、处理时间、理由。三、staging 模型只读取未被隔离或已放行的批次。四、放行必须填写理由；丢弃只改登记状态，不删 raw 中的数据。五、写入身份：登记由 oss911_ingest，放行与丢弃经服务层管理路径由 oss911_admin_svc。</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>一、另建隔离 schema 或隔离表，把坏批次搬过去，放行时再搬回 raw。二、坏批次不入 raw，只记失败日志。</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>一、需要第二份数据副本；放行时「搬回 raw」等于对 raw 做了一次延迟写入，批次的落地时间与原始到达时间分离，回溯困难；搬移过程若中断，同一批数据会两边都有或两边都没有。二、raw 是源端交来什么就记什么的原始记录，「交来过一批坏数据」本身就是要留的事实；不入 raw 则日后无法证明当时收到的是什么（DD-02）。</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>低（新增一张登记表与 staging 的一条过滤条件，不改 raw 结构）</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>REQ-GOV-04 · DD-02 · DD-74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A46"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -710,6 +710,13 @@
       <c r="A46" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-73 至 DD-76 来自第 1 批开发（DDL 落库）。开发机先在临时实例上试建，发现 SQL 本身无误，但缺三样东西：重复执行与版本登记的机制、属主与授权、以及一处 LD-06 与 DDL 的结构矛盾。DD-73 用词定为「结构变更」而非「迁移」，因本项目中「迁移」专指归档数据迁入；并记下一个名字陷阱——meta.schema_version_registry 记的是归档数据源的多版本，不是我方 DDL 版本。DD-74 让 raw 只追加（DD-02）由数据库授权执行而不只靠约定。DD-75 修正 LD-06 2.2：热调记录在结构上写不进 meta.run_log。DD-76 补上 LD-01 7.2 隔离区在 DDL 中缺失的表，并定为「登记」而非「搬移」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-77 把分区粒度由按天改为按月。按天分区从未经决策论证，且 HD-01 REQ-MOD-06 中「按天分区」的写法并非 RFP 要求（1.6.2.5 只要求采用分区）——这是又一处本方措辞被当成客户要求沿用下来的实例，性质与 DD-24、DD-25、DD-38 相同。改在 DDL 落入任何真实环境之前，代价为零。</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5210,6 +5217,48 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DD-77</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>事实表与审计表按月分区，不按天分区</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ddl/05 原为 13 张分区表按 date_key 逐日 RANGE 分区，HD-04 中无任何决策论证该粒度；HD-01 REQ-MOD-06 写作「按天分区」，但 RFP 1.6.2.5 只要求采用分区、未规定粒度，投标响应矩阵亦只承诺 partitioning。数据量：峰值约每日 5 万通呼叫，腿级表每日十余万行。按天分区在合同期八年内约 3.8 万个分区，计入自 2016 年迁入的归档数据后约 8.5 万个。</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>一、13 张分区表一律按月 RANGE 分区，分区键仍为 date_key（YYYYMMDD 整数），一个分区覆盖 [当月 1 日, 次月 1 日)。二、分区函数由 meta.ensure_daily_partitions 改为 meta.ensure_monthly_partitions，仍为幂等、SECURITY DEFINER（DD-74），由编排提前建出未来若干个月。三、月内按日定位依靠已有的 BRIN 索引。四、封账为逻辑冻结：以 close_version 与修正行表达，不改旧行，不依赖分区物理只读——一个月的分区内同时存在已封账与未封账的日子。五、保留期以年计（DD-38），按月卸载分区即可满足。</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>一、按天分区（原设计）。二、按年分区。</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>一、数万个分区在 PostgreSQL 上是实际问题：规划阶段裁不掉分区的查询（通用计划、经连接条件过滤）执行时要锁住每个涉及的分区，易撞上 max_locks_per_transaction 报 out of shared memory；每个连接缓存的分区元数据随之膨胀；归档迁入前须先建 5 万余个分区，autovacuum、统计信息与目录表都要扛数万张小表。而单日数据量仅十余万行，按天切分换不来查询收益——近一年快速路径（DD-36）按月裁剪后月内由 BRIN 定位已足够。二、单分区达千万行级，近一年快速路径的裁剪效果变差；且按年卸载与 DD-38 的保留期边界对不齐。</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>低（此时 ddl/05 只在开发机临时实例中执行过，尚未进入任何真实环境；在 40-schema 落库前修改代价为零，之后则须以新的结构变更重建 13 张分区表）</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>REQ-MOD-06 · REQ-PRF-01 · DD-36 · DD-38 · DD-73 · DD-74</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -713,10 +713,18 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-77 把分区粒度由按天改为按月。按天分区从未经决策论证，且 HD-01 REQ-MOD-06 中「按天分区」的写法并非 RFP 要求（1.6.2.5 只要求采用分区）——这是又一处本方措辞被当成客户要求沿用下来的实例，性质与 DD-24、DD-25、DD-38 相同。改在 DDL 落入任何真实环境之前，代价为零。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-78 更正 DD-77 第三条。DD-77 称「月内按日定位依靠已有的 BRIN 索引」，未经核对：13 张分区表中只有 4 张有 BRIN，date_key 上没有任何索引，而带 BRIN 的接警记录表恰是写入后持续更新、最不适合 BRIN 的表。按维护规则 DD-77 原文不改。DD-78 同时立下一条比索引类型更要紧的规则：按时间范围的查询必须同时带 date_key，否则分区裁剪不生效；归日规则不一致时的后果是静默漏行。</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5259,6 +5267,48 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DD-78</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>分区表的时间列索引按写入模式选择：只追加的表用 BRIN，写入后会被改写的表用 B-tree；更正 DD-77 第三条</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DD-77 第三条写「月内按日定位依靠已有的 BRIN 索引」，与事实不符：13 张分区表中只有 4 张有 BRIN，且没有任何索引建在 date_key 上；而带 BRIN 的 core.fact_intake 恰是写入后会持续更新的表。该句未经核对即写入（2026-10-12 评审发现）。</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>一、判据：行写入后是否还会被改写。只追加、按时间顺序写入 → BRIN；状态推进、结案回填、源端原地更新后重取 → B-tree。二、逐表结论：BRIN 用于 audit.access_log · delivery_log · sla_probe 与 core.fact_call_leg · fact_call · fact_feedback；B-tree 用于 core.fact_intake（created_at，原 BRIN 改为 B-tree）· fact_dispatch_order（issued_at，新增）· fact_turnout（assigned_at，已有）；fact_agent_session 去掉 BRIN，fact_agent_day 新增 (agent_sk, date_key)，fact_ai_inference 与 bridge_call_intake 不单建时间索引。三、凡按时间范围访问分区表的查询必须同时带 date_key 条件，由服务层与 dbt 按 LD-02 第 6 章的归日时区规则翻译。四、增量写入不得改写内容未变的行。五、BRIN 一律 autosummarize = on；归档历史按月、按时间列排序灌入。详见 LD-02 12.1 与 12.2。</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>一、全部分区表统一用 BRIN。二、全部分区表统一用 B-tree。三、不建时间索引，靠月分区裁剪后顺序扫描。</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>一、BRIN 依赖物理顺序与时间顺序一致；被 UPDATE 的行新版本落到表尾或 VACUUM 腾出的旧页空洞，几行错位即撑宽整段摘要，且退化随时间累积，接警与工单两类表会越用越慢。二、只追加的表上 B-tree 的体积与写入代价是 BRIN 的数百倍，换不来查询收益；audit.access_log 量最大，此代价最明显。三、月分区内顺序扫描数十万至数百万行，进不了亚秒档（DD-36），只适用于本表中量很小的三张表。</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>低（索引可随时增删，不改表结构；但规则三若被违反，后果是静默漏行而非报错）</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>REQ-PRF-01 · REQ-MOD-06 · DD-34 · DD-36 · DD-41 · DD-77</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -547,7 +547,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -625,7 +624,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -633,7 +631,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -641,7 +638,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -649,7 +645,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -657,7 +652,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -665,7 +659,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -673,7 +666,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -681,7 +673,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -689,7 +680,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -697,7 +687,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -705,7 +694,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -713,7 +701,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -5285,7 +5272,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>一、判据：行写入后是否还会被改写。只追加、按时间顺序写入 → BRIN；状态推进、结案回填、源端原地更新后重取 → B-tree。二、逐表结论：BRIN 用于 audit.access_log · delivery_log · sla_probe 与 core.fact_call_leg · fact_call · fact_feedback；B-tree 用于 core.fact_intake（created_at，原 BRIN 改为 B-tree）· fact_dispatch_order（issued_at，新增）· fact_turnout（assigned_at，已有）；fact_agent_session 去掉 BRIN，fact_agent_day 新增 (agent_sk, date_key)，fact_ai_inference 与 bridge_call_intake 不单建时间索引。三、凡按时间范围访问分区表的查询必须同时带 date_key 条件，由服务层与 dbt 按 LD-02 第 6 章的归日时区规则翻译。四、增量写入不得改写内容未变的行。五、BRIN 一律 autosummarize = on；归档历史按月、按时间列排序灌入。详见 LD-02 12.1 与 12.2。</t>
+          <t>一、判据：行写入后是否还会被改写。只追加、按时间顺序写入 → BRIN；状态推进、结案回填、源端原地更新后重取 → B-tree。二、逐表结论：BRIN 用于 audit.access_log · delivery_log · sla_probe 与 core.fact_call_leg · fact_call · fact_feedback；B-tree 用于 core.fact_intake（created_at，原 BRIN 改为 B-tree）· fact_dispatch_order（issued_at，新增）· fact_turnout（assigned_at，新增；原仅有覆盖未结案单据的部分索引）；fact_agent_session 去掉 BRIN，fact_agent_day 已有唯一索引 ux_agentday 不另建，fact_ai_inference 与 bridge_call_intake 不单建时间索引。三、凡按时间范围访问分区表的查询必须同时带 date_key 条件，由服务层与 dbt 按 LD-02 第 6 章的归日时区规则翻译。四、增量写入不得改写内容未变的行。五、BRIN 一律 autosummarize = on；归档历史按月、按时间列排序灌入。详见 LD-02 12.1 与 12.2。（同轮定稿时更正两处：初稿称 fact_turnout 的 assigned_at 索引「已有」、fact_agent_day 需「新增」，均系从 ddl/05 抽取索引清单时的模式错误——漏掉了 UNIQUE INDEX，并把部分索引误读为全量索引。由开发机落库前复核指出。）</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -547,6 +547,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -624,6 +625,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -631,6 +633,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -638,6 +641,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -645,6 +649,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -652,6 +657,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -659,6 +665,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -666,6 +673,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -673,6 +681,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -680,6 +689,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -687,6 +697,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -694,6 +705,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -701,6 +713,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -708,10 +721,18 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-78 更正 DD-77 第三条。DD-77 称「月内按日定位依靠已有的 BRIN 索引」，未经核对：13 张分区表中只有 4 张有 BRIN，date_key 上没有任何索引，而带 BRIN 的接警记录表恰是写入后持续更新、最不适合 BRIN 的表。按维护规则 DD-77 原文不改。DD-78 同时立下一条比索引类型更要紧的规则：按时间范围的查询必须同时带 date_key，否则分区裁剪不生效；归日规则不一致时的后果是静默漏行。</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-79 至 DD-81 来自 2026-10-13 的设计评审。DD-79 更正 DD-78 第三条：把查询时间范围一律套到分区键上，会让跨期关闭的单据静默漏掉——这条规则本是为防止静默漏行而立，却换了个原因造成同样的后果。DD-80 统一受控 SQL 的权限语义：此前 LD-04 与 LD-07 两说并存，前者实际无法执行；现定为获授后全库只读，由 MOI 行政管理，本方明示风险。DD-81 区分口径版本与数据版本，使封账后的修正不会被缓存挡住，并让历史报表可指定版本重出。</t>
         </is>
       </c>
     </row>
@@ -1965,7 +1986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5296,6 +5317,132 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DD-79</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>分区条件按归日依据推导：发生日语义带 date_key 范围，关闭日语义不得加 date_key 下界；更正 DD-78 第三条</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DD-78 第三条规定「凡按时间范围访问分区表的查询，必须同时带 date_key 条件」。date_key 是发生日，结案类指标按 closed_date_key（关闭日）归属（LD-03）。查询「10 月结案数」若同时限定发生日在 10 月，9 月发生、10 月关闭的单据即静默消失。2026-10-13 评审指出。</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>一、发生日语义（发生类指标、按发生时间检索）：同时带 date_key 范围与时间列范围。二、关闭日语义（结案类指标、按关闭时间检索）：不加 date_key 下界，只可加安全上界 date_key &lt;= 结束日，由 closed_date_key 索引定位。三、结案类指标的查询 API 走按关闭日聚合的 mart。四、指标属哪一类以 LD-03 分类与指标注册表为准，服务层不自行判断。五、LD-10 增加纪律用例 TC-DISC-04（跨月与跨年关闭）。</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>一、保留 DD-78 的一刀切规则。二、关闭日查询按某个最长处置时长推算 date_key 下界。</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>一、即本条所更正的缺陷：跨期关闭的单据静默漏掉，不报错。二、单据可以开很久，任何固定时长都会在少数长期未结的单据上漏数，而这些往往正是要追究的单据；漏掉不报错。</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>低（改的是查询生成规则，不改表结构）</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>REQ-PRF-01 · REQ-RPT-01 · DD-36 · DD-78</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DD-80</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>受控 SQL 获授后全库只读，不再按字段矩阵与部门过滤限制；授权名单由 MOI 以行政手段管理，本方明示风险</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LD-04 6.2 写「受控 SQL 受字段可见性矩阵与部门行过滤约束」，DD-51 与 LD-07 第 5 章写「被授权人在其范围内可见全量数据」，两说并存；meta.sql_grant 只记录「谁被授权」，没有任何表达「获授哪些数据」的字段。用户自写的 SQL 无法由服务层拼入过滤条件，LD-04 6.2 的说法实际无法执行。2026-10-13 评审指出。</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>一、获授者可见分析副本上的全部业务数据，包括敏感字段，本方不施加范围限制。二、授权名单由 MOI 以行政管理手段控制（DD-51 的自然人显式授权、责任方、MOI 批准保持不变）。三、风险在数据分类政策输入稿中明示：责任方解决的是「谁负责」，不是「能看什么」，不得写成已有技术控制。四、技术护栏照旧：只读、仅走分析副本、超时、结果集上限、导出单独控制。五、LD-04 6.2 旧表述更正。</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>一、按取数档位授权：每档一个数据库只读角色，以列级 GRANT 排除敏感列，sql_grant 增加档位列。二、在档位之上启用行级安全按部门过滤。</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>一、Gavin 决定不采用（2026-10-13）：授权对象是少数经 MOI 批准的自然人，由行政手段管理即可，不为此增加角色与列级授权的维护面。二、REQ-SEC-03 原定行级安全预留不启用；启用即拖慢分析查询，并多一层须维护八年的机制。</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>中（若日后要求按范围授权，须新增数据库角色与列级授权，并改执行器以 SET ROLE 运行；当前 sql_grant 结构可增列兼容）</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>REQ-SEC-02 · REQ-RPT-07 · DD-18 · DD-35 · DD-51</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DD-81</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>缓存与查询区分口径版本与数据版本：缓存键纳入数据发布序号；API 可选最新修正版、原封账版或指定 close_version</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>LD-04 3.3 的缓存键含口径版本与封账状态。封账数据经迟到修正后生成 close_version 加一的行（DD-08 · DD-12），口径版本与封账状态都不变，同一查询会一直命中修正前的结果；API 也无法指定要原封账版还是修正版，历史报表可复现无从兑现。2026-10-13 评审指出。</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>一、mart 每次发布（夜间构建或修正发布）递增一个全局数据发布序号，登记于 meta（表由开发机以结构变更建立）。二、缓存键纳入当前数据发布序号，修正一经发布，旧缓存全部自然失效，无需逐条清除。三、查询参数 version：latest（默认）· as_closed · 指定 close_version。四、响应元字段的版本声明写明所用的数据发布序号与 close_version，打印与导出的报表据此可原样重出。</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>一、发布修正时按受影响的日期范围逐条清缓存。二、缓存键纳入查询范围内的最大 close_version。</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>一、须维护「哪次发布影响了哪些日期」，漏清一条即返回旧数，且不报错。二、每次查缓存前都要先查一次 close_version，抵消了缓存的大半收益。夜间一次发布的节奏下，全局失效的命中率损失可以接受；若日后发布频繁，再改为按日期范围失效。</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>低（缓存键与查询参数的改动，不涉及已有数据）</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>REQ-PRF-01 · REQ-RPT-01 · DD-08 · DD-12 · DD-50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -729,10 +729,18 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-79 至 DD-81 来自 2026-10-13 的设计评审。DD-79 更正 DD-78 第三条：把查询时间范围一律套到分区键上，会让跨期关闭的单据静默漏掉——这条规则本是为防止静默漏行而立，却换了个原因造成同样的后果。DD-80 统一受控 SQL 的权限语义：此前 LD-04 与 LD-07 两说并存，前者实际无法执行；现定为获授后全库只读，由 MOI 行政管理，本方明示风险。DD-81 区分口径版本与数据版本，使封账后的修正不会被缓存挡住，并让历史报表可指定版本重出。</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-82 解决 ICP 契约与 raw 只追加的冲突，并防止 raw 因回看而膨胀 4 至 5 倍：只追加有变化的观测，去重不计被扣下的批次。DD-83 与开发机发现的镜像 digest 问题同源——lock 两份、constraints 校验和只打印不比对，都是「只在纸面上钉死」。钉死一个值，必须有一个环节在它不符时失败，否则写下的值只是注释。</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5443,6 +5451,90 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DD-82</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>raw 只追加有变化的观测：写入前按（幂等键，内容哈希）去重；core 按业务键只接受版本更新且内容有变的观测；坏数据也进 raw 并登记隔离</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ICP 话单契约与 LD-01 写的是「回看区间内按幂等键覆盖写」「时序倒置进隔离区，不进 raw」，与 raw 只追加（DD-02）、坏批次也入 raw（DD-76）及接入角色对 raw 只有 INSERT（DD-74）冲突——照契约实现即无法执行。若改为每次观测都追加，话单每 5 分钟取一次、每次含 15 分钟回看，另有每日回扫，同一张话单约被取到 4 至 5 次，raw 膨胀 4 至 5 倍且多出的全是逐字相同的行。2026-10-13 评审指出冲突，Gavin 指出膨胀。</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>一、raw：写入前查同一（幂等键，内容哈希）是否已存在于正常或已放行的批次中；已存在则不写，否则追加。已结束的话单通常只留一行，取到时尚在变化的留两行。二、去重判断不计待处理与已丢弃批次中的行，使被扣下的观测不挡后续观测（DD-76）。三、同一批次重试取到的内容相同，自然不重复写，不另设去重机制。四、core：按业务键只接受版本更大且内容哈希不同的观测；版本取源端变更时间，源端没有的（如 ICP 话单，结束后不再变化）取观测时间。补数与归档迁入取到的旧快照因版本较小，不会盖掉较新的状态。五、时序倒置等坏数据写入 raw 并登记隔离。六、去重状态即 raw 本身，raw 表须有（幂等键，内容哈希）上的索引；接入角色须能读 meta.quarantine_batch。</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>一、raw 按幂等键覆盖写（原契约）。二、每次观测都追加。三、在 raw 上建（幂等键，内容哈希）唯一约束，以 INSERT … ON CONFLICT DO NOTHING 去重。</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>一、违反 DD-02，且接入角色无 UPDATE 权限，不可执行；覆盖后也无从证明源端曾经给过什么。二、raw 膨胀 4 至 5 倍，多出的行没有证据价值。三、唯一约束不认批次状态：好话单第一次落在被隔离的批次里，后续观测会被约束挡住，该批次一旦丢弃，这张话单就再也回不来。</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>中（影响 raw 表结构与全部接入代码；ICP 话单的 raw 表尚未建，此时定下代价最低）</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>REQ-ING-03 · DD-02 · DD-64 · DD-66 · DD-74 · DD-76</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DD-83</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>dbt 的 lock 以仓库中的 infra/dbt-requirements.lock 为唯一权威，安装直接读它；Airflow constraints 文件的 SHA-256 由剧本断言，不只打印</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>lock 有两份：仓库一份、wheelhouse 一份。30-python 解析时写入 wheelhouse，安装也读 wheelhouse 那份，仓库那份没有被任何环节使用，也没有任何机制保证两份一致。Airflow constraints 文件的 SHA-256 记在 MANIFEST，剧本只打印、不比对。两者都是「只在纸面上钉死」：与容器镜像 digest 写进 inventory 却未经剧本生效是同一类问题（2026-10-13 开发机发现）。</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>一、仓库中的 infra/dbt-requirements.lock 为唯一权威；wheelhouse 不再存 lock 副本，安装以 --requirement 直接读仓库那份、以 --find-links 从 wheelhouse 取轮子。二、升级 dbt 时以显式开关重新解析，结果直接写回仓库路径，由人审 diff 后提交——解析结果是候选，提交才生效。三、Airflow constraints 的 SHA-256 写入 inventory，剧本在安装前断言下载或介质携带的文件与之相同，不符即失败；MANIFEST 引用同一值。四、离网时 infra/ 随介质交付（DD-70），仓库那份 lock 在目标机上本来就有，不需要 wheelhouse 副本。</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>一、以 wheelhouse 那份为准，仓库那份只作备查。二、两份都留，加一个比对断言。</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>一、wheelhouse 是取料产物，不受评审与版本管理；以它为准，等于让一次 pip freeze 的结果不经审阅直接决定生产装什么。二、两份并存本身就是隐患来源，断言只是把「哪份为准」推迟到它们不一致的那一天；而且断言失败时仍须回答以哪份为准。</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>低（只改 30-python 的路径与断言）</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>REQ-OPS-01 · DD-69 · DD-70 · DD-71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -547,7 +547,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -625,7 +624,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -633,7 +631,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -641,7 +638,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -649,7 +645,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -657,7 +652,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -665,7 +659,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -673,7 +666,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -681,7 +673,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -689,7 +680,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -697,7 +687,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -705,7 +694,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -713,7 +701,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -721,7 +708,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -729,7 +715,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -5469,7 +5454,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>一、raw：写入前查同一（幂等键，内容哈希）是否已存在于正常或已放行的批次中；已存在则不写，否则追加。已结束的话单通常只留一行，取到时尚在变化的留两行。二、去重判断不计待处理与已丢弃批次中的行，使被扣下的观测不挡后续观测（DD-76）。三、同一批次重试取到的内容相同，自然不重复写，不另设去重机制。四、core：按业务键只接受版本更大且内容哈希不同的观测；版本取源端变更时间，源端没有的（如 ICP 话单，结束后不再变化）取观测时间。补数与归档迁入取到的旧快照因版本较小，不会盖掉较新的状态。五、时序倒置等坏数据写入 raw 并登记隔离。六、去重状态即 raw 本身，raw 表须有（幂等键，内容哈希）上的索引；接入角色须能读 meta.quarantine_batch。</t>
+          <t>一、raw：写入前查同一（幂等键，内容哈希）是否已存在于正常或已放行的批次中；已存在则不写，否则追加。已结束的话单通常只留一行，取到时尚在变化的留两行。二、去重判断不计待处理与已丢弃批次中的行，使被扣下的观测不挡后续观测（DD-76）。三、同一批次重试取到的内容相同，自然不重复写，不另设去重机制。四、core：按业务键只接受版本更大且内容哈希不同的观测；版本取源端给的版本标识（行级变更时间或数据集级版本号），源端都没有的（如 ICP 话单，结束后不再变化）取观测时间。数据集级版本号（如 ICP 参照数据的 config_version）按快照处理：更大则应用，快照中不再出现的实体置为非当前；相同则不动；更小则不应用、不静默丢弃，进待澄清队列并告警——版本倒退可能是平台回滚，也可能读到滞后节点，须由人判断。补数与归档迁入取到的旧快照因版本较小，不会盖掉较新的状态。五、时序倒置等坏数据写入 raw 并登记隔离。六、去重状态即 raw 本身，raw 表须有（幂等键，内容哈希）上的索引；接入角色须能读 meta.quarantine_batch。（同轮补充，2026-10-13：第四条由「源端变更时间」推广为「源端版本标识」，并写明数据集级版本号的快照规则——由开发机落实 if03d 时提出。）</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -1979,7 +1979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5520,6 +5520,48 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DD-84</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>接入程序为独立 venv 中的命令行程序，由 Airflow 以 BashOperator 调用；退出码 0 含「批次已隔离」，第一版统一有限重试；凭据由子进程自读，属减少暴露而非隔离</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>第 2 批要写接入程序。HD-04 与 LD-01 此前只定了 Airflow 作编排（DD-44）、技术栈含 Python（CN-34），没有定接入程序用什么形态、跑在哪个环境、Airflow 怎么调用。</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>一、Python 命令行程序，装在独立的 venv-ingest，依赖单独冻结为仓库中的 lock（DD-69 · DD-83）。二、Airflow 以 BashOperator 调用，与 dbt 相同；Airflow 只编排。三、退出码：0 成功（含批次被登记隔离），1 运行失败，2 用法或配置错误；不得以 99 退出，BashOperator 一律 skip_on_exit_code=None。四、第一版统一有限次重试，不按退出码分类。五、凭据由接入子进程自读 /etc/oss911/ingest.env。六、详见 LD-01 2.5。</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>一、接入代码装进 Airflow 的 venv，由 PythonOperator 调用。二、在一的基础上把业务代码与 Airflow 解耦。三、为接入程序设独立运行身份与 sudo 受限启动，使 Airflow 无权读取接入口令。四、按退出码区分可重试与不可重试的失败。</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>比较（Gavin 整理，2026-10-13）——依赖：一须与 Airflow 共用依赖、升级要联合验证，所选方案分别冻结分别升级；调用接口：一为函数参数与异常，所选为命令参数与退出码；手工执行：一可以做到但须避免业务代码依赖 Airflow，所选天然适合手工补数与排障；部署成本：一少维护一个环境，所选多一个环境及其 lock；本项目适配：一可行但增加组件耦合，所选与现有 dbt 方式一致。二、可行，但「不依赖 Airflow」只靠纪律维持，不如进程边界可靠。三、DAG 由本方编写、不能经界面提交，DAG 被篡改不在主要威胁之内；多一个系统用户与一条 sudo 规则是要维护八年的权限面。须如实记明：当前的做法只避免 DAG、模板与父进程主动加载口令，同一系统用户仍可读取口令文件，不是隔离。四、BashOperator 不会因退出码不同而采用不同重试策略，要分类须另加机制；而失败时水位不推进、写 raw 按内容去重，统一重试是安全的，最多白跑几次。</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>低（调用方式与环境可调整；退出码约定一经被 DAG 依赖，改动须同步）</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>REQ-ING-01 · REQ-OPS-01 · CN-34 · DD-44 · DD-69 · DD-82 · DD-83</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -547,6 +547,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -624,6 +625,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -631,6 +633,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -638,6 +641,7 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -645,6 +649,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -652,6 +657,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -659,6 +665,7 @@
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -666,6 +673,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -673,6 +681,7 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -680,6 +689,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -687,6 +697,7 @@
         </is>
       </c>
     </row>
+    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -694,6 +705,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -701,6 +713,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -708,6 +721,7 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -715,6 +729,7 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -722,10 +737,18 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-82 解决 ICP 契约与 raw 只追加的冲突，并防止 raw 因回看而膨胀 4 至 5 倍：只追加有变化的观测，去重不计被扣下的批次。DD-83 与开发机发现的镜像 digest 问题同源——lock 两份、constraints 校验和只打印不比对，都是「只在纸面上钉死」。钉死一个值，必须有一个环节在它不符时失败，否则写下的值只是注释。</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【2026-10 补充】DD-84 与 DD-85 定下接入程序的形态与 ETL 节点的高可用。DD-85 补上 LD-08 的一处空白：此前只写了 ETL「成对部署」，没有写两台如何配合。双活成立的前提是 scheduler 无状态，而对任务的要求是能重跑、不依赖在哪台机器上运行、并发受限者用全局 pool——其中第二条在单机开发环境里永远不会暴露。</t>
         </is>
       </c>
     </row>
@@ -1979,7 +2002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5562,6 +5585,48 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DD-85</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ETL-1、ETL-2 上的 Airflow 双活：两台均运行全部组件，LocalExecutor，靠元数据库行锁协调；任务须能重跑、不依赖在哪台机器上运行、并发受限者用全局 pool 约束</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>资源表中 ETL-1..2 只写「Batch orchestration and model builds」，未写明运行 Airflow 与 dbt；LD-08 只写「成对部署」与「跨两台物理主机」（PL-03），没有设计两台如何配合、一台失效会怎样（2026-10-13 Gavin 指出）。</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>一、两台都运行 api-server、scheduler、dag-processor、triggerer，执行器 LocalExecutor，元数据库在 PostgreSQL 集群中的独立数据库（DD-44）。二、scheduler 不保存状态，任务依赖、实例状态与 pool 占用都在元数据库，两个 scheduler 以行锁协调，同一任务不会被两边同时执行。三、一台失效时，其上运行中的任务心跳超时后被标为失败，按重试由另一台重跑。四、任务须满足：能重跑；不依赖在哪台机器上运行——任务之间只经数据库或对象存储交接，不经本地文件；并发受限者用 pool 约束。五、pool icp_cms 与 dbt_build 各 1 个槽位；pool 为全局，非每台各一。六、接入程序另按源持有 PostgreSQL 咨询锁（经会话池），使手工补数也不会与定时任务并发取数。七、测试环境安排一次双节点验证。详见 LD-08 3.3。</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>一、CeleryExecutor。二、主备加虚拟 IP 切换。三、只靠 pool 防止 ICP 并发下载。</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>一、须多一个消息中间件（Redis 或 RabbitMQ），其自身又要做高可用，是又一个须维护八年的组件；本项目的任务量用不着分布式执行。二、要自建故障切换并承担双主风险；Airflow 本身支持多个 scheduler 同时工作，无需另设选主机制。三、pool 只约束经 Airflow 启动的任务，按 DD-84 接入程序可手工执行补数，手工那一次绕过 pool。</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>中（执行器与部署形态改动涉及两台的配置与剧本；三条任务要求一旦被违反，错误为间歇性，难以复现）</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>REQ-AVL-01 · REQ-OPS-01 · PL-03 · DD-44 · DD-67 · DD-82 · DD-84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A56"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -625,7 +624,6 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -633,7 +631,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -641,7 +638,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -649,7 +645,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -657,7 +652,6 @@
         </is>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -665,7 +659,6 @@
         </is>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
@@ -673,7 +666,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -681,7 +673,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
@@ -689,7 +680,6 @@
         </is>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -697,7 +687,6 @@
         </is>
       </c>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
@@ -705,7 +694,6 @@
         </is>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -713,7 +701,6 @@
         </is>
       </c>
     </row>
-    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -721,7 +708,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -729,7 +715,6 @@
         </is>
       </c>
     </row>
-    <row r="51"/>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
@@ -737,7 +722,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
@@ -749,6 +733,13 @@
       <c r="A56" t="inlineStr">
         <is>
           <t>【2026-10 补充】DD-84 与 DD-85 定下接入程序的形态与 ETL 节点的高可用。DD-85 补上 LD-08 的一处空白：此前只写了 ETL「成对部署」，没有写两台如何配合。双活成立的前提是 scheduler 无状态，而对任务的要求是能重跑、不依赖在哪台机器上运行、并发受限者用全局 pool——其中第二条在单机开发环境里永远不会暴露。</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-14：新增 DD-86（接入程序驱动 psycopg 3；LD-09 4.2 增补 LGPL 附条件）；DD-52 所选方案栏加注，指向修订后的 4.2。</t>
         </is>
       </c>
     </row>
@@ -2002,7 +1993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4217,7 +4208,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>新增第五类连接器 mssql_read，驱动链采用 FreeTDS（LGPL）加 unixODBC（LGPL/GPL）加 pyodbc（MIT），或以 pymssql（LGPL，基于 FreeTDS）省去 ODBC 一层。三者均为独立进程或宽松许可的库，符合 LD-09 第 4.2 节的纪律。须在实施前期做一次验证：阿拉伯语字段在 nvarchar 与非 UTF-8 collation 下的读取正确性——FreeTDS 在此历来有坑，不能靠推断。驱动链登记进组件清单，但注明为迁移期组件：对账完成后旧系统下线、IF-01 停用，不需要维护八年；合同期内可能重跑迁移或复核对账，故不删除。</t>
+          <t>新增第五类连接器 mssql_read，驱动链采用 FreeTDS（LGPL）加 unixODBC（LGPL/GPL）加 pyodbc（MIT），或以 pymssql（LGPL，基于 FreeTDS）省去 ODBC 一层。三者均为独立进程或宽松许可的库，符合 LD-09 第 4.2 节的纪律。须在实施前期做一次验证：阿拉伯语字段在 nvarchar 与非 UTF-8 collation 下的读取正确性——FreeTDS 在此历来有坑，不能靠推断。驱动链登记进组件清单，但注明为迁移期组件：对账完成后旧系统下线、IF-01 停用，不需要维护八年；合同期内可能重跑迁移或复核对账，故不删除。 ——【2026-10-14 注】当时 4.2 的白名单未含 LGPL，「符合 4.2」实与原文不符；已由 DD-86 修订 4.2 增补 LGPL（附条件），本条据修订后的 4.2 成立。</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -5624,6 +5615,48 @@
       <c r="H86" t="inlineStr">
         <is>
           <t>REQ-AVL-01 · REQ-OPS-01 · PL-03 · DD-44 · DD-67 · DD-82 · DD-84</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DD-86</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>接入程序的 PostgreSQL 驱动采用 psycopg 3；LD-09 4.2 的白名单增补 LGPL（附条件）</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>接入程序（DD-84）是自研代码，须连接 PostgreSQL。开发机比对 LD-09 4.2 发现：psycopg2 与 psycopg 3 均为 LGPL，不在 4.2 的宽松许可白名单内，按字面不允许 import；同时 DD-52 已采用 FreeTDS 与 pymssql（均 LGPL）却写着「符合 4.2」，规则与既有决策自相矛盾。开发机建议改用 pg8000（BSD-3）。</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>一、修订 LD-09 4.2：白名单增补 LGPL，附三个条件——不修改库源码；只以 import 或动态链接方式使用，不静态链接、不冻结进单文件可执行；组件清单标明并随附许可文本。LGPL 与 GPL 的区别正在于此：它专为让任何许可的程序与之组合而设，传染边界是「用户能否替换该库」，源码加 venv 的交付形态天然满足。GPL 与 AGPL 仍只能以独立进程使用。二、接入程序采用 psycopg 3（新代码不用 legacy 分支；psycopg2 继续由 dbt 独立进程使用，两者并存于 wheelhouse）。三、DD-52 的「符合 4.2」改为依据修订后的 4.2，矛盾消除。四、CLAUDE.md 增加硬约束：自研代码不得打成单文件可执行。</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>一、pg8000（BSD-3，纯 Python）。二、asyncpg（Apache 2.0）。三、维持 4.2 原文不动。</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>一、许可合规，但 LD-09 第 2 节定的选型标准是「上游健康度优先于许可」：pg8000 基本由一人维护，八年合同期内的健康度风险高于作为事实标准的 psycopg；且为一条写严了的规则多引入一个组件，而 4.2 原文的严格程度并无法律依据。二、接入是串行取数，异步接口只增加复杂度。三、维持原文则 DD-52 的 FreeTDS 与 pymssql 同样违规，而连接 SQL Server 没有非 LGPL 的开源驱动链可选，规则本身不可执行。</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>高（驱动是接入程序的基础依赖；但更换驱动只影响接入程序一处，且 4.2 的修订是放宽而非收紧，不影响既有组件）</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>REQ-LIC-03 · REQ-LIC-06 · DD-52 · DD-84 · LD-09 4.2 · LD-09 4.3</t>
         </is>
       </c>
     </row>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A57"/>
+  <dimension ref="A1:A58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -740,6 +740,13 @@
       <c r="A57" t="inlineStr">
         <is>
           <t>2026-10-14：新增 DD-86（接入程序驱动 psycopg 3；LD-09 4.2 增补 LGPL 附条件）；DD-52 所选方案栏加注，指向修订后的 4.2。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-18：新增 DD-87（对象存储经 S3 API 由后端组件访问，接入归档用 boto3）、DD-88（契约同步步骤、热调参数独立表、admin_svc 权限收窄、raw 按月分区）；DD-15 加注。</t>
         </is>
       </c>
     </row>
@@ -1993,7 +2000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H87"/>
+  <dimension ref="A1:H89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2654,7 +2661,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>自建 S3 兼容对象存储，仅由服务层访问</t>
+          <t>自建 S3 兼容对象存储，仅由服务层访问 ——【2026-10-18 注】「仅由服务层访问」指展现层与外部系统不得直连，不排斥本方后端组件；接入程序经 S3 API 归档原文件，见 DD-87。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -5657,6 +5664,90 @@
       <c r="H87" t="inlineStr">
         <is>
           <t>REQ-LIC-03 · REQ-LIC-06 · DD-52 · DD-84 · LD-09 4.2 · LD-09 4.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DD-87</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>对象存储由本方后端组件经 S3 API 访问，接入程序归档原文件用 boto3；修正 DD-15「仅由服务层访问」的措辞</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>LD-01 4.2 与 5.1 要求把收到的原文件归档至对象存储，而 DD-15 写对象存储「仅由服务层访问」，开发机据此无法确定接入程序能否写对象存储；访问方式也未定——S3 协议需 boto3 一类较重依赖或自写 SigV4 签名，SeaweedFS filer 的 HTTP 接口只用标准库但不是 S3。</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>一、DD-15 的「仅由服务层访问」针对的是展现层与外部系统不得直连（与 DD-17 同义），不排斥本方后端组件；措辞修正为「仅由本方后端组件（服务层、接入程序、AI 导出）经 S3 API 访问」。二、接入程序用 boto3（Apache 2.0）经 S3 API 归档，对象键 &lt;源标识&gt;/&lt;run_id&gt;/&lt;batch_seq&gt;；先传对象后提交事务，孤儿对象按 run_id 可查。三、不得使用任何对象存储产品的私有接口——可切换是 DD-15 选型 S3 兼容实现的前提（Gavin 2026-10-18 明确）。四、归档是接入程序的必备步骤，开发期可暂缓，上线前必须就位。</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>一、SeaweedFS filer HTTP 接口（标准库即可）。二、自写 SigV4 签名。三、不归档，以 raw 的 JSONB 原始行代替。</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>一、绑定 SeaweedFS，换对象存储要改接入程序，与「S3 兼容、可切换」的选型前提相悖。二、自行维护签名实现是无谓的安全与维护负担，boto3 是事实标准且许可在白名单内，代价只是 wheelhouse 多十几 MB。三、raw 行是解析后的结果，回答不了「当时收到的到底是什么」（表头、引号、编码、BOM），LD-01 5.1 的理由仍成立。</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>低（只增加一个依赖与一个步骤；DD-15 为措辞修正，不改选型）</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>REQ-MOD-07 · DD-15 · DD-17 · DD-84 · LD-01 2.5 · LD-01 5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DD-88</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>契约由部署步骤同步进库，向前不向后；热调参数独立于契约正文存放；admin_svc 对 meta.source_contract 的 UPDATE 收窄到 enabled 列；raw 表按月分区</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>开发机整理接入程序实现方案时发现：一、meta.source_contract 是「部署时同步的只读副本」（LD-01 2.1），但没有任何步骤写它，而 meta.watermark_state 外键指向它，契约不进库水位推不动；二、M-01 可热调契约中的运行参数（LD-06 2.4），0002 已授 admin_svc 对 source_contract 的 UPDATE，部署同步若整份覆盖 definition 会把热调值冲掉，热调也会污染部署副本；三、LD-02 第 9 章未规定 raw 是否分区，开发机拟先不分区、日后再拷贝重建。</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>一、热调直接改 definition，同步时做 JSON 合并保留热调键。二、raw 先不分区，日后以新结构变更拷贝重建。三、契约由接入程序启动时自行同步。</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>一、合并规则会越写越复杂，且部署副本与仓库文件从此不再逐字相同，失去「库内即部署版本」的可核对性。二、与 DD-77 的论证相同：现在分区是一行配置、代价为零，日后对数亿行只追加的表拷贝重建是以周计的窗口。三、接入程序以 ingest 角色运行，无权写 meta.source_contract，且同步属部署行为，不该发生在每次运行。</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>中（同步步骤与新表为新增；权限收窄涉及一次新结构变更；raw 分区在任何真实数据落地前改，代价为零）</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>REQ-OPS-01 · DD-73 · DD-74 · DD-75 · DD-77 · DD-78 · DD-79 · LD-01 2.1 · LD-01 2.5 · LD-02 第 9 章 · LD-06 2.4 · LD-08 7.2</t>
         </is>
       </c>
     </row>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A58"/>
+  <dimension ref="A1:A59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -747,6 +747,13 @@
       <c r="A58" t="inlineStr">
         <is>
           <t>2026-10-18：新增 DD-87（对象存储经 S3 API 由后端组件访问，接入归档用 boto3）、DD-88（契约同步步骤、热调参数独立表、admin_svc 权限收窄、raw 按月分区）；DD-15 加注。</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-18（同日评审）：DD-88 原地更正五至九条（外键改指 ingest_batch、有效配置快照与白名单、契约同步三支、哈希覆盖范围、性能待验证）；新增 DD-89（放行时间为 staging 第二水位；增量与补数两种模式）。</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H89"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5727,7 +5734,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。</t>
+          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。 ——【2026-10-18 同日评审更正，按 DD-51 先例原地改】五、meta.quarantine_batch 的外键由 run_log 改指向 meta.ingest_batch (run_id, batch_seq)：批次先提交、run_log 最后写，第一批若需隔离时父记录尚不存在。六、有效配置在运行开始时解析一次、整个运行沿用，热调项快照写入 ingest_batch.effective_params；热调白名单（参数名、类型、范围）写入 source_runtime_param 的 CHECK；启停只认 source_contract.enabled，白名单不含启停；第一版轮询间隔为发布项、不可热调（接入程序读参数改变不了 DAG 触发频率，LD-06 2.4 随之更正）。七、契约同步分三支：同版本同内容不动、同版本不同内容部署失败并提示递增版本、文件版本低于库内拒绝；新版本同步前按新白名单校验既有热调值，不兼容则部署失败列出参数，不自动作废。八、内容哈希覆盖实际收到的完整字段名与原值，不限于契约已登记列。九、分区去重性能列为待验证（LD-10 TC-ING-01），不预先宣布可接受。</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5748,6 +5755,48 @@
       <c r="H89" t="inlineStr">
         <is>
           <t>REQ-OPS-01 · DD-73 · DD-74 · DD-75 · DD-77 · DD-78 · DD-79 · LD-01 2.1 · LD-01 2.5 · LD-02 第 9 章 · LD-06 2.4 · LD-08 7.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DD-89</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>staging 按批次消费 raw，以隔离放行时间为第二水位；接入程序分增量与手工补数两种模式，补数不动水位</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-10-18 评审指出两处遗漏：一、LD-02 第 9 章新写「staging 增量按 ingested_at 推进」，但被隔离的批次放行后 ingested_at 仍是旧值，按时间增量永远不会再被选中——周一入 raw 被隔离、staging 推进到周三、周四放行，那批数据就此丢在 raw 里。二、LD-01 2.5 只写「每批推进水位」，未区分日常增量与手工补数，补历史会把水位调回去，补未来某段会越过中间缺口。</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>一、staging 取两类批次的并集：未隔离且 ingested_at 大于上次处理位置的；quarantine_batch 中 state = released 且 handled_at 大于上次处理位置的。staging 行记 staged_at 作上次处理位置。放行成为显式的补处理入口，M-03 放行界面已要求显示重算范围。二、增量模式窗口起点恒为水位减回看、按批前推、水位只前进、由构造连续；手工补数模式带显式起止，ingest_batch.mode = backfill，不动水位。两种模式共用 raw、去重与隔离规则。</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>一、放行时由 M-03 直接触发一次针对该批次的 dbt 运行。二、放行时把该批次 raw 行的 ingested_at 改为放行时间。三、补数也推进水位，取 max(水位, 补数终点)。</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>一、把数据变更的触发权放进管理界面，且 M-03 以 admin_svc 身份无权也不该运行 dbt；第二水位让下一次常规 staging 运行自然带上它，不需要新的触发链路。二、改 raw 即违反只追加（DD-02），且销毁「何时收到」的事实。三、补未来某段会把水位推过中间缺口，缺口从此静默。</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>低（staging 多一个过滤分支与一列 staged_at；接入程序多一个模式参数）</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>DD-02 · DD-76 · DD-82 · DD-88 · LD-01 2.5 · LD-01 7.2 · LD-02 第 9 章 · LD-06 第 3 章</t>
         </is>
       </c>
     </row>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A59"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -754,6 +754,13 @@
       <c r="A59" t="inlineStr">
         <is>
           <t>2026-10-18（同日评审）：DD-88 原地更正五至九条（外键改指 ingest_batch、有效配置快照与白名单、契约同步三支、哈希覆盖范围、性能待验证）；新增 DD-89（放行时间为 staging 第二水位；增量与补数两种模式）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-19：新增 DD-90（CAD 中间库：本方托管、DS 写入、结构原样、触发器时间戳）；DD-04、DD-61 加注。</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2206,7 +2213,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>选择读原生基表，映射写在我方 dbt 模型中，配以映射三态登记与验证样例</t>
+          <t>选择读原生基表，映射写在我方 dbt 模型中，配以映射三态登记与验证样例 ——【2026-10-19 注】DD-90 接受 DS 写入本方托管的中间库，但结构仍为 CAD 原样、DDL 由 DS 交付，不是本条所拒的「我方定义结构」；本条四条理由仍然成立并作为 DD-90 的边界条件。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -4600,7 +4607,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>一、基线维持水位轮询（REQ-ING-02）。CDC 唯一不可替代的优势是亚秒延迟与变更捕获，而本系统的延迟要求为分钟级，不需要前者；后者以第二条补偿。 二、无论 CDC 是否谈成，增设滚动窗口校验：近 30 天按日分区比对源端与本方的行数与关键列哈希，差异进待澄清队列。这是不上 CDC 时对物理删除与静默更新唯一现实的补偿，代价为每日一次源端分区级扫描。 三、把逻辑复制作为备选正式列入 IR-02 向 DS 提出，不由本方代为判断对方会拒绝。若 DS 同意，需其提供：wal_level=logical（改此参数要重启展示库）、带 REPLICATION 属性的角色与建槽权限（现仅谈只读 SELECT 账号，见 IR-06）、并维护 PUBLICATION 随 CAD 结构变更。槽的有状态性可用 max_slot_wal_keep_size（PG 13 起）封顶，超限时槽失效而非源端磁盘耗尽，风险由「本方停机可能影响 CAD 展示库」降为「本方需重新全量同步」。若展示库本身为物理备库，逻辑解码需 PG 16 起支持，版本待确认。 四、同批需问清展示库是否存在整表重载式的 ETL 刷新——若有，CDC 会产生海量伪变更，水位轮询同样失效，两种方案都要改。</t>
+          <t>一、基线维持水位轮询（REQ-ING-02）。CDC 唯一不可替代的优势是亚秒延迟与变更捕获，而本系统的延迟要求为分钟级，不需要前者；后者以第二条补偿。 二、无论 CDC 是否谈成，增设滚动窗口校验：近 30 天按日分区比对源端与本方的行数与关键列哈希，差异进待澄清队列。这是不上 CDC 时对物理删除与静默更新唯一现实的补偿，代价为每日一次源端分区级扫描。 三、把逻辑复制作为备选正式列入 IR-02 向 DS 提出，不由本方代为判断对方会拒绝。若 DS 同意，需其提供：wal_level=logical（改此参数要重启展示库）、带 REPLICATION 属性的角色与建槽权限（现仅谈只读 SELECT 账号，见 IR-06）、并维护 PUBLICATION 随 CAD 结构变更。槽的有状态性可用 max_slot_wal_keep_size（PG 13 起）封顶，超限时槽失效而非源端磁盘耗尽，风险由「本方停机可能影响 CAD 展示库」降为「本方需重新全量同步」。若展示库本身为物理备库，逻辑解码需 PG 16 起支持，版本待确认。 四、同批需问清展示库是否存在整表重载式的 ETL 刷新——若有，CDC 会产生海量伪变更，水位轮询同样失效，两种方案都要改。 ——【2026-10-19 注】DD-90 将 CAD 增量源改为本方托管的中间库，变更捕获改用本方触发器时间戳，逻辑复制的三项前提与「展示库为 PostgreSQL」的依赖均消失；滚动窗口校验保留为加固措施。本条原文保留。</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5797,6 +5804,48 @@
       <c r="H90" t="inlineStr">
         <is>
           <t>DD-02 · DD-76 · DD-82 · DD-88 · LD-01 2.5 · LD-01 7.2 · LD-02 第 9 章 · LD-06 第 3 章</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>DD-90</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CAD 增量源改为本方托管、DS 写入的中间库：本方 PostgreSQL 集群内单独 database cad_mirror，结构为 CAD 74 张表原样、DDL 由 DS 交付，DS 按主键 UPSERT 写入；变更捕获改用本方触发器时间戳</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>DS 对 CAD 问题单的答复（2026-10-15）称展示库为 SQL Server，与约定的 PostgreSQL 不符，Gavin 定按约定要求 PG。DS 随后提出：由本方按标准建中间库与视图，DS 写入。需判断这是否就是 DD-04 当年否掉的「我方定义结构、DS 写入」。</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>一、坚持 DS 自建 PostgreSQL 展示库、本方出向只读。二、单独一套 PG 实例承载中间库。三、接受 SQL Server 展示库，IF-02 改 mssql_read。四、由本方定义结构、DS 映射写入（即 DD-04 所拒）。</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>一、可行但劣于中间库：sjc 不可靠与 CDC 三项前提都要 DS 配合，而中间库在本方手里这两个问题自行消失；DS 又已表示愿意写入。二、隔离更彻底，但多一套要维护八年的实例，按每日数万行的量不值；同集群单独 database 已足够隔离凭据与权限。三、与约定不符，且 sjc 问题仍在、CDC 备选变成 SQL Server 特性。四、DD-04 的四条理由全部仍然成立。</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>中（接口点与网络边界变化；但结构原样、连接器不变、raw 不变，代码层改动小）</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>REQ-ING-02 · DD-02 · DD-04 · DD-58 · DD-61 · DD-74 · IR-02 · IR-50 · IR-51 · IR-52 · LD-01 第 3 章 · LD-07 2.1 · LD-08 第 8 章</t>
         </is>
       </c>
     </row>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A60"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -761,6 +761,13 @@
       <c r="A60" t="inlineStr">
         <is>
           <t>2026-10-19：新增 DD-90（CAD 中间库：本方托管、DS 写入、结构原样、触发器时间戳）；DD-04、DD-61 加注。</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-19（同日评审第二轮）：DD-89 原地更正（staging 按批次登记，非时间位置）；DD-90 原地更正（心跳围栏、回扫维持必需、写入角色最小权限）。</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5790,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>一、staging 取两类批次的并集：未隔离且 ingested_at 大于上次处理位置的；quarantine_batch 中 state = released 且 handled_at 大于上次处理位置的。staging 行记 staged_at 作上次处理位置。放行成为显式的补处理入口，M-03 放行界面已要求显示重算范围。二、增量模式窗口起点恒为水位减回看、按批前推、水位只前进、由构造连续；手工补数模式带显式起止，ingest_batch.mode = backfill，不动水位。两种模式共用 raw、去重与隔离规则。</t>
+          <t>一、staging 取两类批次的并集：未隔离且 ingested_at 大于上次处理位置的；quarantine_batch 中 state = released 且 handled_at 大于上次处理位置的。staging 行记 staged_at 作上次处理位置。放行成为显式的补处理入口，M-03 放行界面已要求显示重算范围。二、增量模式窗口起点恒为水位减回看、按批前推、水位只前进、由构造连续；手工补数模式带显式起止，ingest_batch.mode = backfill，不动水位。两种模式共用 raw、去重与隔离规则。 ——【2026-10-19 同日评审更正，原地改】一的「staging 行记 staged_at 作上次处理位置」不成立：查询 10:00、放行 10:01、staging 10:02 完成并记位置，10:01 的放行永远跳过。改为按批次登记：meta.staging_batch_state（model、run_id、batch_seq、staged_at），取「可处理且本模型未登记」的批次，登记与模型写入同一事务；时间水位只用于缩小扫描，不作判据。</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5825,7 +5832,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。</t>
+          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。 ——【2026-10-19 同日评审更正，原地改】四、触发器时间戳不是提交时间（now() 更是事务开始时间），不能据此把回扫降级：窗口上界改取最新心跳的 started_at（DS 周期串行、心跳后写，故为提交围栏）；writer 角色设 statement_timeout 与 idle_in_transaction_session_timeout；8.3 回扫维持必需项，待 TC-ING-02 通过再议。二、写入角色不是属主：cad_mirror 由 NOLOGIN 的 cad_mirror_owner 持有，cad_mirror_writer 只有 CONNECT、USAGE、cad.* 的 SELECT/INSERT/UPDATE、cad_meta.* 的 INSERT，无 CREATE/DELETE/TRUNCATE/TRIGGER。</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -768,6 +768,13 @@
       <c r="A61" t="inlineStr">
         <is>
           <t>2026-10-19（同日评审第二轮）：DD-89 原地更正（staging 按批次登记，非时间位置）；DD-90 原地更正（心跳围栏、回扫维持必需、写入角色最小权限）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-19（0004 落地）：DD-88 补记十至十三（分区函数扩到 raw、run_log outcome 三值、白名单首版、ingest_batch 两列与 raw 外键）；IR-51 补四项；中间库规范 v0.3 加 3.6 转换要求。</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5755,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。 ——【2026-10-18 同日评审更正，按 DD-51 先例原地改】五、meta.quarantine_batch 的外键由 run_log 改指向 meta.ingest_batch (run_id, batch_seq)：批次先提交、run_log 最后写，第一批若需隔离时父记录尚不存在。六、有效配置在运行开始时解析一次、整个运行沿用，热调项快照写入 ingest_batch.effective_params；热调白名单（参数名、类型、范围）写入 source_runtime_param 的 CHECK；启停只认 source_contract.enabled，白名单不含启停；第一版轮询间隔为发布项、不可热调（接入程序读参数改变不了 DAG 触发频率，LD-06 2.4 随之更正）。七、契约同步分三支：同版本同内容不动、同版本不同内容部署失败并提示递增版本、文件版本低于库内拒绝；新版本同步前按新白名单校验既有热调值，不兼容则部署失败列出参数，不自动作废。八、内容哈希覆盖实际收到的完整字段名与原值，不限于契约已登记列。九、分区去重性能列为待验证（LD-10 TC-ING-01），不预先宣布可接受。</t>
+          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。 ——【2026-10-18 同日评审更正，按 DD-51 先例原地改】五、meta.quarantine_batch 的外键由 run_log 改指向 meta.ingest_batch (run_id, batch_seq)：批次先提交、run_log 最后写，第一批若需隔离时父记录尚不存在。六、有效配置在运行开始时解析一次、整个运行沿用，热调项快照写入 ingest_batch.effective_params；热调白名单（参数名、类型、范围）写入 source_runtime_param 的 CHECK；启停只认 source_contract.enabled，白名单不含启停；第一版轮询间隔为发布项、不可热调（接入程序读参数改变不了 DAG 触发频率，LD-06 2.4 随之更正）。七、契约同步分三支：同版本同内容不动、同版本不同内容部署失败并提示递增版本、文件版本低于库内拒绝；新版本同步前按新白名单校验既有热调值，不兼容则部署失败列出参数，不自动作废。八、内容哈希覆盖实际收到的完整字段名与原值，不限于契约已登记列。九、分区去重性能列为待验证（LD-10 TC-ING-01），不预先宣布可接受。 ——【2026-10-19 0004 落地补记】十、meta.ensure_monthly_partitions 的范围由 core · audit 扩大到 raw（0002 曾收窄；raw 按月分区后须以属主身份建分区，接入角色不得自建）；timestamptz 分区键 ingested_at 的月边界取 UTC 月初零点并带显式偏移——它是系统时间，无业务日含义，不适用 LD-02 第 6 章的归日时区。十一、meta.run_log.outcome 只表达提交状态：success / partial / failed；quarantined 不再使用但不改 CHECK，隔离情况由 M-01 关联 meta.quarantine_batch 呈现，不混入 outcome。十二、热调白名单第一版只有 lookback_minutes（1–1440）；批量与限流待第一份用到它们的契约随结构变更加入。十三、ingest_batch 另有 rows_written 与 received_header 两列；raw 每行带指向 ingest_batch 的外键。</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A62"/>
+  <dimension ref="A1:A63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -775,6 +775,13 @@
       <c r="A62" t="inlineStr">
         <is>
           <t>2026-10-19（0004 落地）：DD-88 补记十至十三（分区函数扩到 raw、run_log outcome 三值、白名单首版、ingest_batch 两列与 raw 外键）；IR-51 补四项；中间库规范 v0.3 加 3.6 转换要求。</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-19：DD-90 补记——CAD 自身为 PG，DDL 不转换；被拒方案五逻辑复制（生产库风险，Gavin 定）。规范 v0.4。</t>
         </is>
       </c>
     </row>
@@ -5839,17 +5846,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。 ——【2026-10-19 同日评审更正，原地改】四、触发器时间戳不是提交时间（now() 更是事务开始时间），不能据此把回扫降级：窗口上界改取最新心跳的 started_at（DS 周期串行、心跳后写，故为提交围栏）；writer 角色设 statement_timeout 与 idle_in_transaction_session_timeout；8.3 回扫维持必需项，待 TC-ING-02 通过再议。二、写入角色不是属主：cad_mirror 由 NOLOGIN 的 cad_mirror_owner 持有，cad_mirror_writer 只有 CONNECT、USAGE、cad.* 的 SELECT/INSERT/UPDATE、cad_meta.* 的 INSERT，无 CREATE/DELETE/TRUNCATE/TRIGGER。</t>
+          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。 ——【2026-10-19 同日评审更正，原地改】四、触发器时间戳不是提交时间（now() 更是事务开始时间），不能据此把回扫降级：窗口上界改取最新心跳的 started_at（DS 周期串行、心跳后写，故为提交围栏）；writer 角色设 statement_timeout 与 idle_in_transaction_session_timeout；8.3 回扫维持必需项，待 TC-ING-02 通过再议。二、写入角色不是属主：cad_mirror 由 NOLOGIN 的 cad_mirror_owner 持有，cad_mirror_writer 只有 CONNECT、USAGE、cad.* 的 SELECT/INSERT/UPDATE、cad_meta.* 的 INSERT，无 CREATE/DELETE/TRUNCATE/TRIGGER。 ——【2026-10-19 补记】CAD 自身的库为 PostgreSQL（SQL Server 为上一代 BI 附带的中间层），中间库 DDL 不需要跨产品转换：取 CAD 原库 PG DDL 原样、只改名。规范 v0.3 的 3.6 节（SQL Server→PG 十处差异）在 v0.4 中撤回，IR-51 相应更正。</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>一、坚持 DS 自建 PostgreSQL 展示库、本方出向只读。二、单独一套 PG 实例承载中间库。三、接受 SQL Server 展示库，IF-02 改 mssql_read。四、由本方定义结构、DS 映射写入（即 DD-04 所拒）。</t>
+          <t>一、坚持 DS 自建 PostgreSQL 展示库、本方出向只读。二、单独一套 PG 实例承载中间库。三、接受 SQL Server 展示库，IF-02 改 mssql_read。四、由本方定义结构、DS 映射写入（即 DD-04 所拒）。 五、PostgreSQL 逻辑复制：CAD 原库建 PUBLICATION、cad_mirror 建 SUBSCRIPTION（2026-10-19 得知 CAD 自身即为 PG 后提出）。</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>一、可行但劣于中间库：sjc 不可靠与 CDC 三项前提都要 DS 配合，而中间库在本方手里这两个问题自行消失；DS 又已表示愿意写入。二、隔离更彻底，但多一套要维护八年的实例，按每日数万行的量不值；同集群单独 database 已足够隔离凭据与权限。三、与约定不符，且 sjc 问题仍在、CDC 备选变成 SQL Server 特性。四、DD-04 的四条理由全部仍然成立。</t>
+          <t>一、可行但劣于中间库：sjc 不可靠与 CDC 三项前提都要 DS 配合，而中间库在本方手里这两个问题自行消失；DS 又已表示愿意写入。二、隔离更彻底，但多一套要维护八年的实例，按每日数万行的量不值；同集群单独 database 已足够隔离凭据与权限。三、与约定不符，且 sjc 问题仍在、CDC 备选变成 SQL Server 特性。四、DD-04 的四条理由全部仍然成立。 五、技术上优于程序写入（按提交顺序到达、无需心跳围栏、网络为出向、DS 几乎不写代码），但要在 CAD 生产库上开 wal_level = logical 并重启，复制槽在 CAD 侧占 WAL，本方长时间断开会撑其磁盘——拖垮生产库的风险由对方承担，Gavin 2026-10-19 明确不采用。中间库由 DS 程序写入的方案不变。</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -782,6 +782,13 @@
       <c r="A63" t="inlineStr">
         <is>
           <t>2026-10-19：DD-90 补记——CAD 自身为 PG，DDL 不转换；被拒方案五逻辑复制（生产库风险，Gavin 定）。规范 v0.4。</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-19（评审第四轮）：DD-88 补记十四至十六（单一契约校验、回看只能调大、同步加锁）。</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5769,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。 ——【2026-10-18 同日评审更正，按 DD-51 先例原地改】五、meta.quarantine_batch 的外键由 run_log 改指向 meta.ingest_batch (run_id, batch_seq)：批次先提交、run_log 最后写，第一批若需隔离时父记录尚不存在。六、有效配置在运行开始时解析一次、整个运行沿用，热调项快照写入 ingest_batch.effective_params；热调白名单（参数名、类型、范围）写入 source_runtime_param 的 CHECK；启停只认 source_contract.enabled，白名单不含启停；第一版轮询间隔为发布项、不可热调（接入程序读参数改变不了 DAG 触发频率，LD-06 2.4 随之更正）。七、契约同步分三支：同版本同内容不动、同版本不同内容部署失败并提示递增版本、文件版本低于库内拒绝；新版本同步前按新白名单校验既有热调值，不兼容则部署失败列出参数，不自动作废。八、内容哈希覆盖实际收到的完整字段名与原值，不限于契约已登记列。九、分区去重性能列为待验证（LD-10 TC-ING-01），不预先宣布可接受。 ——【2026-10-19 0004 落地补记】十、meta.ensure_monthly_partitions 的范围由 core · audit 扩大到 raw（0002 曾收窄；raw 按月分区后须以属主身份建分区，接入角色不得自建）；timestamptz 分区键 ingested_at 的月边界取 UTC 月初零点并带显式偏移——它是系统时间，无业务日含义，不适用 LD-02 第 6 章的归日时区。十一、meta.run_log.outcome 只表达提交状态：success / partial / failed；quarantined 不再使用但不改 CHECK，隔离情况由 M-01 关联 meta.quarantine_batch 呈现，不混入 outcome。十二、热调白名单第一版只有 lookback_minutes（1–1440）；批量与限流待第一份用到它们的契约随结构变更加入。十三、ingest_batch 另有 rows_written 与 received_header 两列；raw 每行带指向 ingest_batch 的外键。</t>
+          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。 ——【2026-10-18 同日评审更正，按 DD-51 先例原地改】五、meta.quarantine_batch 的外键由 run_log 改指向 meta.ingest_batch (run_id, batch_seq)：批次先提交、run_log 最后写，第一批若需隔离时父记录尚不存在。六、有效配置在运行开始时解析一次、整个运行沿用，热调项快照写入 ingest_batch.effective_params；热调白名单（参数名、类型、范围）写入 source_runtime_param 的 CHECK；启停只认 source_contract.enabled，白名单不含启停；第一版轮询间隔为发布项、不可热调（接入程序读参数改变不了 DAG 触发频率，LD-06 2.4 随之更正）。七、契约同步分三支：同版本同内容不动、同版本不同内容部署失败并提示递增版本、文件版本低于库内拒绝；新版本同步前按新白名单校验既有热调值，不兼容则部署失败列出参数，不自动作废。八、内容哈希覆盖实际收到的完整字段名与原值，不限于契约已登记列。九、分区去重性能列为待验证（LD-10 TC-ING-01），不预先宣布可接受。 ——【2026-10-19 0004 落地补记】十、meta.ensure_monthly_partitions 的范围由 core · audit 扩大到 raw（0002 曾收窄；raw 按月分区后须以属主身份建分区，接入角色不得自建）；timestamptz 分区键 ingested_at 的月边界取 UTC 月初零点并带显式偏移——它是系统时间，无业务日含义，不适用 LD-02 第 6 章的归日时区。十一、meta.run_log.outcome 只表达提交状态：success / partial / failed；quarantined 不再使用但不改 CHECK，隔离情况由 M-01 关联 meta.quarantine_batch 呈现，不混入 outcome。十二、热调白名单第一版只有 lookback_minutes（1–1440）；批量与限流待第一份用到它们的契约随结构变更加入。十三、ingest_batch 另有 rows_written 与 received_header 两列；raw 每行带指向 ingest_batch 的外键。 ——【2026-10-19 评审第四轮】十四、契约校验只有一套，在接入程序内，部署与 M-01 调用它；最小校验集与 YAML 重复键拒绝见 LD-01 2.5。十五、热调的回看长度只能调大、不得小于契约默认值（缩短只少数据不报错）；调小走发布。0004 的 CHECK 不改，规则在校验代码里。十六、契约同步事务加 pg_advisory_xact_lock 串行化。</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -789,6 +789,13 @@
       <c r="A64" t="inlineStr">
         <is>
           <t>2026-10-19（评审第四轮）：DD-88 补记十四至十六（单一契约校验、回看只能调大、同步加锁）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-21（评审第五轮）：DD-88 补记十七至十九（行锁协议、同一快照、必填层校验）。</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5776,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。 ——【2026-10-18 同日评审更正，按 DD-51 先例原地改】五、meta.quarantine_batch 的外键由 run_log 改指向 meta.ingest_batch (run_id, batch_seq)：批次先提交、run_log 最后写，第一批若需隔离时父记录尚不存在。六、有效配置在运行开始时解析一次、整个运行沿用，热调项快照写入 ingest_batch.effective_params；热调白名单（参数名、类型、范围）写入 source_runtime_param 的 CHECK；启停只认 source_contract.enabled，白名单不含启停；第一版轮询间隔为发布项、不可热调（接入程序读参数改变不了 DAG 触发频率，LD-06 2.4 随之更正）。七、契约同步分三支：同版本同内容不动、同版本不同内容部署失败并提示递增版本、文件版本低于库内拒绝；新版本同步前按新白名单校验既有热调值，不兼容则部署失败列出参数，不自动作废。八、内容哈希覆盖实际收到的完整字段名与原值，不限于契约已登记列。九、分区去重性能列为待验证（LD-10 TC-ING-01），不预先宣布可接受。 ——【2026-10-19 0004 落地补记】十、meta.ensure_monthly_partitions 的范围由 core · audit 扩大到 raw（0002 曾收窄；raw 按月分区后须以属主身份建分区，接入角色不得自建）；timestamptz 分区键 ingested_at 的月边界取 UTC 月初零点并带显式偏移——它是系统时间，无业务日含义，不适用 LD-02 第 6 章的归日时区。十一、meta.run_log.outcome 只表达提交状态：success / partial / failed；quarantined 不再使用但不改 CHECK，隔离情况由 M-01 关联 meta.quarantine_batch 呈现，不混入 outcome。十二、热调白名单第一版只有 lookback_minutes（1–1440）；批量与限流待第一份用到它们的契约随结构变更加入。十三、ingest_batch 另有 rows_written 与 received_header 两列；raw 每行带指向 ingest_batch 的外键。 ——【2026-10-19 评审第四轮】十四、契约校验只有一套，在接入程序内，部署与 M-01 调用它；最小校验集与 YAML 重复键拒绝见 LD-01 2.5。十五、热调的回看长度只能调大、不得小于契约默认值（缩短只少数据不报错）；调小走发布。0004 的 CHECK 不改，规则在校验代码里。十六、契约同步事务加 pg_advisory_xact_lock 串行化。</t>
+          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。 ——【2026-10-18 同日评审更正，按 DD-51 先例原地改】五、meta.quarantine_batch 的外键由 run_log 改指向 meta.ingest_batch (run_id, batch_seq)：批次先提交、run_log 最后写，第一批若需隔离时父记录尚不存在。六、有效配置在运行开始时解析一次、整个运行沿用，热调项快照写入 ingest_batch.effective_params；热调白名单（参数名、类型、范围）写入 source_runtime_param 的 CHECK；启停只认 source_contract.enabled，白名单不含启停；第一版轮询间隔为发布项、不可热调（接入程序读参数改变不了 DAG 触发频率，LD-06 2.4 随之更正）。七、契约同步分三支：同版本同内容不动、同版本不同内容部署失败并提示递增版本、文件版本低于库内拒绝；新版本同步前按新白名单校验既有热调值，不兼容则部署失败列出参数，不自动作废。八、内容哈希覆盖实际收到的完整字段名与原值，不限于契约已登记列。九、分区去重性能列为待验证（LD-10 TC-ING-01），不预先宣布可接受。 ——【2026-10-19 0004 落地补记】十、meta.ensure_monthly_partitions 的范围由 core · audit 扩大到 raw（0002 曾收窄；raw 按月分区后须以属主身份建分区，接入角色不得自建）；timestamptz 分区键 ingested_at 的月边界取 UTC 月初零点并带显式偏移——它是系统时间，无业务日含义，不适用 LD-02 第 6 章的归日时区。十一、meta.run_log.outcome 只表达提交状态：success / partial / failed；quarantined 不再使用但不改 CHECK，隔离情况由 M-01 关联 meta.quarantine_batch 呈现，不混入 outcome。十二、热调白名单第一版只有 lookback_minutes（1–1440）；批量与限流待第一份用到它们的契约随结构变更加入。十三、ingest_batch 另有 rows_written 与 received_header 两列；raw 每行带指向 ingest_batch 的外键。 ——【2026-10-19 评审第四轮】十四、契约校验只有一套，在接入程序内，部署与 M-01 调用它；最小校验集与 YAML 重复键拒绝见 LD-01 2.5。十五、热调的回看长度只能调大、不得小于契约默认值（缩短只少数据不报错）；调小走发布。0004 的 CHECK 不改，规则在校验代码里。十六、契约同步事务加 pg_advisory_xact_lock 串行化。 ——【2026-10-21 评审第五轮】十七、部署同步对契约行 FOR UPDATE、M-01 对同一行 FOR SHARE，堵住部署与热调之间的竞态（advisory lock 只管部署之间）；十八、接入启动时契约与覆盖值同一快照读取；十九、校验分通用层与按连接器的必填层，必填缺失为配置错误、退出码 2。</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -796,6 +796,13 @@
       <c r="A65" t="inlineStr">
         <is>
           <t>2026-10-21（评审第五轮）：DD-88 补记十七至十九（行锁协议、同一快照、必填层校验）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-24：DD-84 注（DAG 生成与运行参数）、DD-85 注（Airflow 密钥受管）。</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5615,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>一、Python 命令行程序，装在独立的 venv-ingest，依赖单独冻结为仓库中的 lock（DD-69 · DD-83）。二、Airflow 以 BashOperator 调用，与 dbt 相同；Airflow 只编排。三、退出码：0 成功（含批次被登记隔离），1 运行失败，2 用法或配置错误；不得以 99 退出，BashOperator 一律 skip_on_exit_code=None。四、第一版统一有限次重试，不按退出码分类。五、凭据由接入子进程自读 /etc/oss911/ingest.env。六、详见 LD-01 2.5。</t>
+          <t>一、Python 命令行程序，装在独立的 venv-ingest，依赖单独冻结为仓库中的 lock（DD-69 · DD-83）。二、Airflow 以 BashOperator 调用，与 dbt 相同；Airflow 只编排。三、退出码：0 成功（含批次被登记隔离），1 运行失败，2 用法或配置错误；不得以 99 退出，BashOperator 一律 skip_on_exit_code=None。四、第一版统一有限次重试，不按退出码分类。五、凭据由接入子进程自读 /etc/oss911/ingest.env。六、详见 LD-01 2.5。 ——【2026-10-24 注】DAG 由发布清单生成、一源一 DAG，不读契约 YAML（LD-01 2.1）；pool 映射在清单中；max_active_runs=1、catchup=False；任务超时首版 30 分钟，按批提交保证超时只丢当前批；增量模式无水位即退出码 2；新 DAG 人工开启为首次上线验收步骤，重复部署不改暂停状态。</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5650,7 +5657,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>一、两台都运行 api-server、scheduler、dag-processor、triggerer，执行器 LocalExecutor，元数据库在 PostgreSQL 集群中的独立数据库（DD-44）。二、scheduler 不保存状态，任务依赖、实例状态与 pool 占用都在元数据库，两个 scheduler 以行锁协调，同一任务不会被两边同时执行。三、一台失效时，其上运行中的任务心跳超时后被标为失败，按重试由另一台重跑。四、任务须满足：能重跑；不依赖在哪台机器上运行——任务之间只经数据库或对象存储交接，不经本地文件；并发受限者用 pool 约束。五、pool icp_cms 与 dbt_build 各 1 个槽位；pool 为全局，非每台各一。六、接入程序另按源持有 PostgreSQL 咨询锁（经会话池），使手工补数也不会与定时任务并发取数。七、测试环境安排一次双节点验证。详见 LD-08 3.3。</t>
+          <t>一、两台都运行 api-server、scheduler、dag-processor、triggerer，执行器 LocalExecutor，元数据库在 PostgreSQL 集群中的独立数据库（DD-44）。二、scheduler 不保存状态，任务依赖、实例状态与 pool 占用都在元数据库，两个 scheduler 以行锁协调，同一任务不会被两边同时执行。三、一台失效时，其上运行中的任务心跳超时后被标为失败，按重试由另一台重跑。四、任务须满足：能重跑；不依赖在哪台机器上运行——任务之间只经数据库或对象存储交接，不经本地文件；并发受限者用 pool 约束。五、pool icp_cms 与 dbt_build 各 1 个槽位；pool 为全局，非每台各一。六、接入程序另按源持有 PostgreSQL 咨询锁（经会话池），使手工补数也不会与定时任务并发取数。七、测试环境安排一次双节点验证。详见 LD-08 3.3。 ——【2026-10-24 注】补一条前提：jwt_secret 与 fernet_key 须为各节点共享的受管配置（剧本生成一次、airflow.env 同一份），否则双活下任务汇报与口令解密间歇性失败。开发机发现（2026-10-24）。</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A66"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -803,6 +803,13 @@
       <c r="A66" t="inlineStr">
         <is>
           <t>2026-10-24：DD-84 注（DAG 生成与运行参数）、DD-85 注（Airflow 密钥受管）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-25：DD-90 条件一更正（DDL 由本方生成、DS 核对）；IR-51 相应更正；规范 v0.5。</t>
         </is>
       </c>
     </row>
@@ -5867,7 +5874,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。 ——【2026-10-19 同日评审更正，原地改】四、触发器时间戳不是提交时间（now() 更是事务开始时间），不能据此把回扫降级：窗口上界改取最新心跳的 started_at（DS 周期串行、心跳后写，故为提交围栏）；writer 角色设 statement_timeout 与 idle_in_transaction_session_timeout；8.3 回扫维持必需项，待 TC-ING-02 通过再议。二、写入角色不是属主：cad_mirror 由 NOLOGIN 的 cad_mirror_owner 持有，cad_mirror_writer 只有 CONNECT、USAGE、cad.* 的 SELECT/INSERT/UPDATE、cad_meta.* 的 INSERT，无 CREATE/DELETE/TRUNCATE/TRIGGER。 ——【2026-10-19 补记】CAD 自身的库为 PostgreSQL（SQL Server 为上一代 BI 附带的中间层），中间库 DDL 不需要跨产品转换：取 CAD 原库 PG DDL 原样、只改名。规范 v0.3 的 3.6 节（SQL Server→PG 十处差异）在 v0.4 中撤回，IR-51 相应更正。</t>
+          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。 ——【2026-10-19 同日评审更正，原地改】四、触发器时间戳不是提交时间（now() 更是事务开始时间），不能据此把回扫降级：窗口上界改取最新心跳的 started_at（DS 周期串行、心跳后写，故为提交围栏）；writer 角色设 statement_timeout 与 idle_in_transaction_session_timeout；8.3 回扫维持必需项，待 TC-ING-02 通过再议。二、写入角色不是属主：cad_mirror 由 NOLOGIN 的 cad_mirror_owner 持有，cad_mirror_writer 只有 CONNECT、USAGE、cad.* 的 SELECT/INSERT/UPDATE、cad_meta.* 的 INSERT，无 CREATE/DELETE/TRUNCATE/TRIGGER。 ——【2026-10-19 补记】CAD 自身的库为 PostgreSQL（SQL Server 为上一代 BI 附带的中间层），中间库 DDL 不需要跨产品转换：取 CAD 原库 PG DDL 原样、只改名。规范 v0.3 的 3.6 节（SQL Server→PG 十处差异）在 v0.4 中撤回，IR-51 相应更正。 ——【2026-10-25 更正条件一】上一代中间库的 DDL 由当时的 BI 方建、DS 只写入（Gavin 告知），故 DDL 改为由本方按《Bill同步CAD表数据结构》生成、DS 核对会签。DD-04 的边界由此只能靠本方自律：74 张表全部列照建、一列不少、不加任何本方模型的东西；类型映射宁宽勿严（text / timestamp / numeric），收紧放在 staging。另向 DS 索取 CAD 原库完整目录，判断结构表是否为上一代 BI 选定的子集。</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A67"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -810,6 +810,13 @@
       <c r="A67" t="inlineStr">
         <is>
           <t>2026-10-25：DD-90 条件一更正（DDL 由本方生成、DS 核对）；IR-51 相应更正；规范 v0.5。</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-26：DD-73/74/85/89/90 加注（cad_mirror 独立序列与开发期重建、CONNECT 收回、密钥权威来源、resweep 逻辑日期、触发器与改名列）；规范 v0.6。</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5167,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>一、用词定为「结构变更」（DDL change），不叫「迁移」——本项目中「迁移」专指 Hexagon 归档数据迁入（CN-15 · CN-16 · REQ-MIG-* · DD-37 · DD-57 至 DD-60），沿用行业惯例的 migration 会在交接检索时混成两类毫不相干的东西。二、清单 ddl/changes.yml 记「编号 → 文件列表」；ddl/01..05 原样作为变更 0001（LD-02 按文件名引用它们，不挪不改名）；此后的变更放 ddl/changes/。三、登记表 meta.ddl_change（变更 0000），一个变更一行，记文件列表与拼接后的 SHA-256；与 meta.release_registry（DD-49，一次发布一行）并列，一对多。四、每个变更的全部文件连同登记行在同一个事务中执行。五、已执行变更的文件校验和一旦变了，执行器必须失败并报出新旧校验和——结构只能新增变更来改，与登记册「不改写、只新增」同一条规矩。回退亦以新增一个反向变更实现，不撤销已执行的变更。六、执行器为 Ansible + psql，不另写工具。七、0000 至 0002 以超级用户执行（0001 建扩展，0002 建角色）；0003 起事务开头 SET LOCAL ROLE oss911_owner，新对象归属主。</t>
+          <t>一、用词定为「结构变更」（DDL change），不叫「迁移」——本项目中「迁移」专指 Hexagon 归档数据迁入（CN-15 · CN-16 · REQ-MIG-* · DD-37 · DD-57 至 DD-60），沿用行业惯例的 migration 会在交接检索时混成两类毫不相干的东西。二、清单 ddl/changes.yml 记「编号 → 文件列表」；ddl/01..05 原样作为变更 0001（LD-02 按文件名引用它们，不挪不改名）；此后的变更放 ddl/changes/。三、登记表 meta.ddl_change（变更 0000），一个变更一行，记文件列表与拼接后的 SHA-256；与 meta.release_registry（DD-49，一次发布一行）并列，一对多。四、每个变更的全部文件连同登记行在同一个事务中执行。五、已执行变更的文件校验和一旦变了，执行器必须失败并报出新旧校验和——结构只能新增变更来改，与登记册「不改写、只新增」同一条规矩。回退亦以新增一个反向变更实现，不撤销已执行的变更。六、执行器为 Ansible + psql，不另写工具。七、0000 至 0002 以超级用户执行（0001 建扩展，0002 建角色）；0003 起事务开头 SET LOCAL ROLE oss911_owner，新对象归属主。 ——【2026-10-26 注，Gavin 定】cad_mirror 另起一套变更序列（ddl/cad_mirror/changes.yml，登记表在该库的 ddl schema），不进 oss911 的序列；开发阶段允许改写已执行的变更并整库重建（cad_mirror_rebuild），自正式软件发布起（inventory cad_mirror_ddl_frozen）才适用「执行过不能改」。生成器 tools/cad_mirror_ddl.py 自此由开发机维护。</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5202,7 +5209,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>一、五个 NOLOGIN 权限角色：oss911_owner 持有 raw · core · meta · audit 全部对象与七个 schema；oss911_ingest 对 raw 只有 SELECT 与 INSERT，并写 meta 中的水位、运行日志、值剖析与映射登记；oss911_transform（dbt）对 raw 只读，对 core 可增删改但不能 DROP，staging · mart · ai 由它在运行时建并归它所有；oss911_query_svc 读 core · mart · ai · meta，对 audit 只 INSERT 访问与投递留痕；oss911_admin_svc 继承 query_svc，另写权限矩阵与参照配置表及其变更留痕，可查 audit（M-07）。二、可登录用户与口令按环境由剧本建立并加入相应角色；变更 0002 随发布制品进入生产，不得含口令或环境相关的用户名。三、ALTER DEFAULT PRIVILEGES 只管授权、不管属主——它保证新对象自动授权给其他角色，但不改变属主是谁。四、meta.ensure_daily_partitions 改为 SECURITY DEFINER（search_path 钉死），收窄到 core 与 audit 的分区表，EXECUTE 只授 oss911_transform：建分区要求调用者是父表属主，而编排调用时不是。五、写权限只授有依据的；依据不明者本次不授，代码写到时以新增变更补，并在提交说明里写明依据。由此产生三条硬约束：dbt profile 必须设 role: oss911_transform；core 模型只能以增量写入既有表（dbt 不是属主，--full-refresh 会失败，这是期望的行为）；raw 表必须由结构变更建，接入程序不得自建（属主天然拥有 DELETE 与 TRUNCATE）。新角色不需要改 pgbouncer 的 userlist.txt，其余用户经 auth_query 现查。</t>
+          <t>一、五个 NOLOGIN 权限角色：oss911_owner 持有 raw · core · meta · audit 全部对象与七个 schema；oss911_ingest 对 raw 只有 SELECT 与 INSERT，并写 meta 中的水位、运行日志、值剖析与映射登记；oss911_transform（dbt）对 raw 只读，对 core 可增删改但不能 DROP，staging · mart · ai 由它在运行时建并归它所有；oss911_query_svc 读 core · mart · ai · meta，对 audit 只 INSERT 访问与投递留痕；oss911_admin_svc 继承 query_svc，另写权限矩阵与参照配置表及其变更留痕，可查 audit（M-07）。二、可登录用户与口令按环境由剧本建立并加入相应角色；变更 0002 随发布制品进入生产，不得含口令或环境相关的用户名。三、ALTER DEFAULT PRIVILEGES 只管授权、不管属主——它保证新对象自动授权给其他角色，但不改变属主是谁。四、meta.ensure_daily_partitions 改为 SECURITY DEFINER（search_path 钉死），收窄到 core 与 audit 的分区表，EXECUTE 只授 oss911_transform：建分区要求调用者是父表属主，而编排调用时不是。五、写权限只授有依据的；依据不明者本次不授，代码写到时以新增变更补，并在提交说明里写明依据。由此产生三条硬约束：dbt profile 必须设 role: oss911_transform；core 模型只能以增量写入既有表（dbt 不是属主，--full-refresh 会失败，这是期望的行为）；raw 表必须由结构变更建，接入程序不得自建（属主天然拥有 DELETE 与 TRUNCATE）。新角色不需要改 pgbouncer 的 userlist.txt，其余用户经 auth_query 现查。 ——【2026-10-26 注】各库 CONNECT 从 PUBLIC 收回、只授使用者（LD-07 2.1）。开发机实测发现 DS 写入账号能连 oss911，「零权限」此前只在纸面成立。</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5664,7 +5671,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>一、两台都运行 api-server、scheduler、dag-processor、triggerer，执行器 LocalExecutor，元数据库在 PostgreSQL 集群中的独立数据库（DD-44）。二、scheduler 不保存状态，任务依赖、实例状态与 pool 占用都在元数据库，两个 scheduler 以行锁协调，同一任务不会被两边同时执行。三、一台失效时，其上运行中的任务心跳超时后被标为失败，按重试由另一台重跑。四、任务须满足：能重跑；不依赖在哪台机器上运行——任务之间只经数据库或对象存储交接，不经本地文件；并发受限者用 pool 约束。五、pool icp_cms 与 dbt_build 各 1 个槽位；pool 为全局，非每台各一。六、接入程序另按源持有 PostgreSQL 咨询锁（经会话池），使手工补数也不会与定时任务并发取数。七、测试环境安排一次双节点验证。详见 LD-08 3.3。 ——【2026-10-24 注】补一条前提：jwt_secret 与 fernet_key 须为各节点共享的受管配置（剧本生成一次、airflow.env 同一份），否则双活下任务汇报与口令解密间歇性失败。开发机发现（2026-10-24）。</t>
+          <t>一、两台都运行 api-server、scheduler、dag-processor、triggerer，执行器 LocalExecutor，元数据库在 PostgreSQL 集群中的独立数据库（DD-44）。二、scheduler 不保存状态，任务依赖、实例状态与 pool 占用都在元数据库，两个 scheduler 以行锁协调，同一任务不会被两边同时执行。三、一台失效时，其上运行中的任务心跳超时后被标为失败，按重试由另一台重跑。四、任务须满足：能重跑；不依赖在哪台机器上运行——任务之间只经数据库或对象存储交接，不经本地文件；并发受限者用 pool 约束。五、pool icp_cms 与 dbt_build 各 1 个槽位；pool 为全局，非每台各一。六、接入程序另按源持有 PostgreSQL 咨询锁（经会话池），使手工补数也不会与定时任务并发取数。七、测试环境安排一次双节点验证。详见 LD-08 3.3。 ——【2026-10-24 注】补一条前提：jwt_secret 与 fernet_key 须为各节点共享的受管配置（剧本生成一次、airflow.env 同一份），否则双活下任务汇报与口令解密间歇性失败。开发机发现（2026-10-24）。 ——【2026-10-26 注】密钥的权威来源只有控制节点一份，分发后启动前断言一致；逐台纳管不构成「共享配置」。</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5832,7 +5839,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>一、staging 取两类批次的并集：未隔离且 ingested_at 大于上次处理位置的；quarantine_batch 中 state = released 且 handled_at 大于上次处理位置的。staging 行记 staged_at 作上次处理位置。放行成为显式的补处理入口，M-03 放行界面已要求显示重算范围。二、增量模式窗口起点恒为水位减回看、按批前推、水位只前进、由构造连续；手工补数模式带显式起止，ingest_batch.mode = backfill，不动水位。两种模式共用 raw、去重与隔离规则。 ——【2026-10-19 同日评审更正，原地改】一的「staging 行记 staged_at 作上次处理位置」不成立：查询 10:00、放行 10:01、staging 10:02 完成并记位置，10:01 的放行永远跳过。改为按批次登记：meta.staging_batch_state（model、run_id、batch_seq、staged_at），取「可处理且本模型未登记」的批次，登记与模型写入同一事务；时间水位只用于缩小扫描，不作判据。</t>
+          <t>一、staging 取两类批次的并集：未隔离且 ingested_at 大于上次处理位置的；quarantine_batch 中 state = released 且 handled_at 大于上次处理位置的。staging 行记 staged_at 作上次处理位置。放行成为显式的补处理入口，M-03 放行界面已要求显示重算范围。二、增量模式窗口起点恒为水位减回看、按批前推、水位只前进、由构造连续；手工补数模式带显式起止，ingest_batch.mode = backfill，不动水位。两种模式共用 raw、去重与隔离规则。 ——【2026-10-19 同日评审更正，原地改】一的「staging 行记 staged_at 作上次处理位置」不成立：查询 10:00、放行 10:01、staging 10:02 完成并记位置，10:01 的放行永远跳过。改为按批次登记：meta.staging_batch_state（model、run_id、batch_seq、staged_at），取「可处理且本模型未登记」的批次，登记与模型写入同一事务；时间水位只用于缩小扫描，不作判据。 ——【2026-10-26 注】resweep 为第三种模式：窗口由 DAG 按逻辑日期传入、回扫 DAG catchup = true、不动水位；无末腿统计分「已收到」与「可用」两个口径，后者排除 pending / discarded。</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5874,7 +5881,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。 ——【2026-10-19 同日评审更正，原地改】四、触发器时间戳不是提交时间（now() 更是事务开始时间），不能据此把回扫降级：窗口上界改取最新心跳的 started_at（DS 周期串行、心跳后写，故为提交围栏）；writer 角色设 statement_timeout 与 idle_in_transaction_session_timeout；8.3 回扫维持必需项，待 TC-ING-02 通过再议。二、写入角色不是属主：cad_mirror 由 NOLOGIN 的 cad_mirror_owner 持有，cad_mirror_writer 只有 CONNECT、USAGE、cad.* 的 SELECT/INSERT/UPDATE、cad_meta.* 的 INSERT，无 CREATE/DELETE/TRUNCATE/TRIGGER。 ——【2026-10-19 补记】CAD 自身的库为 PostgreSQL（SQL Server 为上一代 BI 附带的中间层），中间库 DDL 不需要跨产品转换：取 CAD 原库 PG DDL 原样、只改名。规范 v0.3 的 3.6 节（SQL Server→PG 十处差异）在 v0.4 中撤回，IR-51 相应更正。 ——【2026-10-25 更正条件一】上一代中间库的 DDL 由当时的 BI 方建、DS 只写入（Gavin 告知），故 DDL 改为由本方按《Bill同步CAD表数据结构》生成、DS 核对会签。DD-04 的边界由此只能靠本方自律：74 张表全部列照建、一列不少、不加任何本方模型的东西；类型映射宁宽勿严（text / timestamp / numeric），收紧放在 staging。另向 DS 索取 CAD 原库完整目录，判断结构表是否为上一代 BI 选定的子集。</t>
+          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。 ——【2026-10-19 同日评审更正，原地改】四、触发器时间戳不是提交时间（now() 更是事务开始时间），不能据此把回扫降级：窗口上界改取最新心跳的 started_at（DS 周期串行、心跳后写，故为提交围栏）；writer 角色设 statement_timeout 与 idle_in_transaction_session_timeout；8.3 回扫维持必需项，待 TC-ING-02 通过再议。二、写入角色不是属主：cad_mirror 由 NOLOGIN 的 cad_mirror_owner 持有，cad_mirror_writer 只有 CONNECT、USAGE、cad.* 的 SELECT/INSERT/UPDATE、cad_meta.* 的 INSERT，无 CREATE/DELETE/TRUNCATE/TRIGGER。 ——【2026-10-19 补记】CAD 自身的库为 PostgreSQL（SQL Server 为上一代 BI 附带的中间层），中间库 DDL 不需要跨产品转换：取 CAD 原库 PG DDL 原样、只改名。规范 v0.3 的 3.6 节（SQL Server→PG 十处差异）在 v0.4 中撤回，IR-51 相应更正。 ——【2026-10-25 更正条件一】上一代中间库的 DDL 由当时的 BI 方建、DS 只写入（Gavin 告知），故 DDL 改为由本方按《Bill同步CAD表数据结构》生成、DS 核对会签。DD-04 的边界由此只能靠本方自律：74 张表全部列照建、一列不少、不加任何本方模型的东西；类型映射宁宽勿严（text / timestamp / numeric），收紧放在 staging。另向 DS 索取 CAD 原库完整目录，判断结构表是否为上一代 BI 选定的子集。 ——【2026-10-26 注】触发器对内容相同的 UPDATE 不写新行版本、不动时间戳（DD-78 的同一原则），UPSERT 因此回报 0 行是有意的，已写进规范 v0.6；21 个保留字列名改名不加引号，两处重名列待 DS 给译名；水位列改 B-tree（UPSERT 原地改写）。</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A68"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -817,6 +817,13 @@
       <c r="A68" t="inlineStr">
         <is>
           <t>2026-10-26：DD-73/74/85/89/90 加注（cad_mirror 独立序列与开发期重建、CONNECT 收回、密钥权威来源、resweep 逻辑日期、触发器与改名列）；规范 v0.6。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-27：新增 DD-91（core 装载规则十二处）、DD-92（caller_number_hash 算法，先留空）；LD-10 三条用例编号改为 TC-DISC-19/20/21（原编号与 test/cases_seed.csv 冲突）。</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5419,7 +5426,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>一、发生日语义（发生类指标、按发生时间检索）：同时带 date_key 范围与时间列范围。二、关闭日语义（结案类指标、按关闭时间检索）：不加 date_key 下界，只可加安全上界 date_key &lt;= 结束日，由 closed_date_key 索引定位。三、结案类指标的查询 API 走按关闭日聚合的 mart。四、指标属哪一类以 LD-03 分类与指标注册表为准，服务层不自行判断。五、LD-10 增加纪律用例 TC-DISC-04（跨月与跨年关闭）。</t>
+          <t>一、发生日语义（发生类指标、按发生时间检索）：同时带 date_key 范围与时间列范围。二、关闭日语义（结案类指标、按关闭时间检索）：不加 date_key 下界，只可加安全上界 date_key &lt;= 结束日，由 closed_date_key 索引定位。三、结案类指标的查询 API 走按关闭日聚合的 mart。四、指标属哪一类以 LD-03 分类与指标注册表为准，服务层不自行判断。五、LD-10 增加纪律用例 TC-DISC-19（跨月与跨年关闭）。</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5797,7 +5804,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。 ——【2026-10-18 同日评审更正，按 DD-51 先例原地改】五、meta.quarantine_batch 的外键由 run_log 改指向 meta.ingest_batch (run_id, batch_seq)：批次先提交、run_log 最后写，第一批若需隔离时父记录尚不存在。六、有效配置在运行开始时解析一次、整个运行沿用，热调项快照写入 ingest_batch.effective_params；热调白名单（参数名、类型、范围）写入 source_runtime_param 的 CHECK；启停只认 source_contract.enabled，白名单不含启停；第一版轮询间隔为发布项、不可热调（接入程序读参数改变不了 DAG 触发频率，LD-06 2.4 随之更正）。七、契约同步分三支：同版本同内容不动、同版本不同内容部署失败并提示递增版本、文件版本低于库内拒绝；新版本同步前按新白名单校验既有热调值，不兼容则部署失败列出参数，不自动作废。八、内容哈希覆盖实际收到的完整字段名与原值，不限于契约已登记列。九、分区去重性能列为待验证（LD-10 TC-ING-01），不预先宣布可接受。 ——【2026-10-19 0004 落地补记】十、meta.ensure_monthly_partitions 的范围由 core · audit 扩大到 raw（0002 曾收窄；raw 按月分区后须以属主身份建分区，接入角色不得自建）；timestamptz 分区键 ingested_at 的月边界取 UTC 月初零点并带显式偏移——它是系统时间，无业务日含义，不适用 LD-02 第 6 章的归日时区。十一、meta.run_log.outcome 只表达提交状态：success / partial / failed；quarantined 不再使用但不改 CHECK，隔离情况由 M-01 关联 meta.quarantine_batch 呈现，不混入 outcome。十二、热调白名单第一版只有 lookback_minutes（1–1440）；批量与限流待第一份用到它们的契约随结构变更加入。十三、ingest_batch 另有 rows_written 与 received_header 两列；raw 每行带指向 ingest_batch 的外键。 ——【2026-10-19 评审第四轮】十四、契约校验只有一套，在接入程序内，部署与 M-01 调用它；最小校验集与 YAML 重复键拒绝见 LD-01 2.5。十五、热调的回看长度只能调大、不得小于契约默认值（缩短只少数据不报错）；调小走发布。0004 的 CHECK 不改，规则在校验代码里。十六、契约同步事务加 pg_advisory_xact_lock 串行化。 ——【2026-10-21 评审第五轮】十七、部署同步对契约行 FOR UPDATE、M-01 对同一行 FOR SHARE，堵住部署与热调之间的竞态（advisory lock 只管部署之间）；十八、接入启动时契约与覆盖值同一快照读取；十九、校验分通用层与按连接器的必填层，必填缺失为配置错误、退出码 2。</t>
+          <t>一、同步由部署做：40-schema 之后新增一步，以属主身份把 contracts/ 下的 YAML 写入 meta.source_contract，只写 definition、contract_version、target_raw、connector，且只在文件版本号大于库内时写（向前不向后，与 LD-08 7.2 同一规则）。二、新建 meta.source_runtime_param（source_id、参数名、值、更新时间、更新人），M-01 的四类热调项（启停、间隔、批量、限流）写这里并留痕于 audit.runtime_param_change_log；enabled 列属启停，同步永不触碰。接入程序读 definition 再叠加 runtime_param。三、新结构变更把 admin_svc 对 source_contract 的 UPDATE 收窄为 UPDATE (enabled)，其余撤销（0002 已执行，不改原文件）。四、raw 表按月分区，键为 ingested_at，索引按 DD-78（见 LD-02 第 9 章）。 ——【2026-10-18 同日评审更正，按 DD-51 先例原地改】五、meta.quarantine_batch 的外键由 run_log 改指向 meta.ingest_batch (run_id, batch_seq)：批次先提交、run_log 最后写，第一批若需隔离时父记录尚不存在。六、有效配置在运行开始时解析一次、整个运行沿用，热调项快照写入 ingest_batch.effective_params；热调白名单（参数名、类型、范围）写入 source_runtime_param 的 CHECK；启停只认 source_contract.enabled，白名单不含启停；第一版轮询间隔为发布项、不可热调（接入程序读参数改变不了 DAG 触发频率，LD-06 2.4 随之更正）。七、契约同步分三支：同版本同内容不动、同版本不同内容部署失败并提示递增版本、文件版本低于库内拒绝；新版本同步前按新白名单校验既有热调值，不兼容则部署失败列出参数，不自动作废。八、内容哈希覆盖实际收到的完整字段名与原值，不限于契约已登记列。九、分区去重性能列为待验证（LD-10 TC-DISC-20），不预先宣布可接受。 ——【2026-10-19 0004 落地补记】十、meta.ensure_monthly_partitions 的范围由 core · audit 扩大到 raw（0002 曾收窄；raw 按月分区后须以属主身份建分区，接入角色不得自建）；timestamptz 分区键 ingested_at 的月边界取 UTC 月初零点并带显式偏移——它是系统时间，无业务日含义，不适用 LD-02 第 6 章的归日时区。十一、meta.run_log.outcome 只表达提交状态：success / partial / failed；quarantined 不再使用但不改 CHECK，隔离情况由 M-01 关联 meta.quarantine_batch 呈现，不混入 outcome。十二、热调白名单第一版只有 lookback_minutes（1–1440）；批量与限流待第一份用到它们的契约随结构变更加入。十三、ingest_batch 另有 rows_written 与 received_header 两列；raw 每行带指向 ingest_batch 的外键。 ——【2026-10-19 评审第四轮】十四、契约校验只有一套，在接入程序内，部署与 M-01 调用它；最小校验集与 YAML 重复键拒绝见 LD-01 2.5。十五、热调的回看长度只能调大、不得小于契约默认值（缩短只少数据不报错）；调小走发布。0004 的 CHECK 不改，规则在校验代码里。十六、契约同步事务加 pg_advisory_xact_lock 串行化。 ——【2026-10-21 评审第五轮】十七、部署同步对契约行 FOR UPDATE、M-01 对同一行 FOR SHARE，堵住部署与热调之间的竞态（advisory lock 只管部署之间）；十八、接入启动时契约与覆盖值同一快照读取；十九、校验分通用层与按连接器的必填层，必填缺失为配置错误、退出码 2。</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5881,7 +5888,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。 ——【2026-10-19 同日评审更正，原地改】四、触发器时间戳不是提交时间（now() 更是事务开始时间），不能据此把回扫降级：窗口上界改取最新心跳的 started_at（DS 周期串行、心跳后写，故为提交围栏）；writer 角色设 statement_timeout 与 idle_in_transaction_session_timeout；8.3 回扫维持必需项，待 TC-ING-02 通过再议。二、写入角色不是属主：cad_mirror 由 NOLOGIN 的 cad_mirror_owner 持有，cad_mirror_writer 只有 CONNECT、USAGE、cad.* 的 SELECT/INSERT/UPDATE、cad_meta.* 的 INSERT，无 CREATE/DELETE/TRUNCATE/TRIGGER。 ——【2026-10-19 补记】CAD 自身的库为 PostgreSQL（SQL Server 为上一代 BI 附带的中间层），中间库 DDL 不需要跨产品转换：取 CAD 原库 PG DDL 原样、只改名。规范 v0.3 的 3.6 节（SQL Server→PG 十处差异）在 v0.4 中撤回，IR-51 相应更正。 ——【2026-10-25 更正条件一】上一代中间库的 DDL 由当时的 BI 方建、DS 只写入（Gavin 告知），故 DDL 改为由本方按《Bill同步CAD表数据结构》生成、DS 核对会签。DD-04 的边界由此只能靠本方自律：74 张表全部列照建、一列不少、不加任何本方模型的东西；类型映射宁宽勿严（text / timestamp / numeric），收紧放在 staging。另向 DS 索取 CAD 原库完整目录，判断结构表是否为上一代 BI 选定的子集。 ——【2026-10-26 注】触发器对内容相同的 UPDATE 不写新行版本、不动时间戳（DD-78 的同一原则），UPSERT 因此回报 0 行是有意的，已写进规范 v0.6；21 个保留字列名改名不加引号，两处重名列待 DS 给译名；水位列改 B-tree（UPSERT 原地改写）。</t>
+          <t>一、接受，但结构必须是 CAD 原样（Table Lists 英文视图名、翻译列名、全部列不筛选），DDL 由 DS 定义与交付、本方只审不改——这与 DD-04 否掉的方案差一个词：那是我方模型由 DS 映射，这是源端原样换个地方放，raw「源端交来什么就记什么」不变。二、同集群单独 database cad_mirror（Gavin 2026-10-19 定），写入角色 cad_mirror_writer 仅为该库属主，对 oss911 零权限；经 pgBouncer session 模式单独池写入。三、写入方式按主键 UPSERT，不 TRUNCATE、不整表重载；DS 每周期写心跳表。四、每表加 mirror_updated_at 列由触发器维护，作为水位列，sjc 不可靠（Q10）由此解决；8.3 滚动窗口校验降回加固措施。五、中间库即交接点，中间库与 CAD 一致由 DS 负责；DS 定期提供 CAD 源端按日计数供本方对账。六、入向网络通道须 MOI 批（IR-52）。七、规范发 DS 会签（queries/CAD_Mirror_Database_Specification.docx），空白项为 IR-51。 ——【2026-10-19 同日评审更正，原地改】四、触发器时间戳不是提交时间（now() 更是事务开始时间），不能据此把回扫降级：窗口上界改取最新心跳的 started_at（DS 周期串行、心跳后写，故为提交围栏）；writer 角色设 statement_timeout 与 idle_in_transaction_session_timeout；8.3 回扫维持必需项，待 TC-DISC-21 通过再议。二、写入角色不是属主：cad_mirror 由 NOLOGIN 的 cad_mirror_owner 持有，cad_mirror_writer 只有 CONNECT、USAGE、cad.* 的 SELECT/INSERT/UPDATE、cad_meta.* 的 INSERT，无 CREATE/DELETE/TRUNCATE/TRIGGER。 ——【2026-10-19 补记】CAD 自身的库为 PostgreSQL（SQL Server 为上一代 BI 附带的中间层），中间库 DDL 不需要跨产品转换：取 CAD 原库 PG DDL 原样、只改名。规范 v0.3 的 3.6 节（SQL Server→PG 十处差异）在 v0.4 中撤回，IR-51 相应更正。 ——【2026-10-25 更正条件一】上一代中间库的 DDL 由当时的 BI 方建、DS 只写入（Gavin 告知），故 DDL 改为由本方按《Bill同步CAD表数据结构》生成、DS 核对会签。DD-04 的边界由此只能靠本方自律：74 张表全部列照建、一列不少、不加任何本方模型的东西；类型映射宁宽勿严（text / timestamp / numeric），收紧放在 staging。另向 DS 索取 CAD 原库完整目录，判断结构表是否为上一代 BI 选定的子集。 ——【2026-10-26 注】触发器对内容相同的 UPDATE 不写新行版本、不动时间戳（DD-78 的同一原则），UPSERT 因此回报 0 行是有意的，已写进规范 v0.6；21 个保留字列名改名不加引号，两处重名列待 DS 给译名；水位列改 B-tree（UPSERT 原地改写）。</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5902,6 +5909,90 @@
       <c r="H91" t="inlineStr">
         <is>
           <t>REQ-ING-02 · DD-02 · DD-04 · DD-58 · DD-61 · DD-74 · IR-02 · IR-50 · IR-51 · IR-52 · LD-01 第 3 章 · LD-07 2.1 · LD-08 第 8 章</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>DD-91</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>core 装载规则十二处：src_system 按系统取值（icp · cad · cad_archive）、站点 MKK 以结构变更写入、维度迟到留空不造成员、CHECK 增 unmapped、释放原因归类进契约、src_observed_at 与派生内容哈希决定写入、date_key 变化按 sk 跨分区先删后插、transform 可写待澄清队列、tz 偏移取契约约定、分区预建三个月、dbt 独立 DAG 同频运行</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>开发机写 dbt 前逐条核对 LD-02、DD-06/66/74/77/78/79/82/89 与契约，发现十二处设计空白或冲突，其中代理键的 src_system 一经上线不可改（2026-10-26 NOTES）。</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>见 LD-02 第 3 章末补充段的十二条。要点：src_system 按系统不按源，使同一系统的坐席工号在维度与事实上算出同一键；归档单独为 cad_archive，以免割接并行期与 CAD 撞键；unmapped 是 DD-06「未映射不得归入其他」在 CHECK 上的落实；写入判定按 core 行派生内容而非源端原文，否则归类表更正与维度补齐永远写不进去；dbt 不接在增量 DAG 之后，因同一 DAG 内 max_active_runs = 1 会让 dbt 重试堵住接入。</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>一、src_system 按源（icp_cdr_voice）。二、维度缺席时造「未知坐席」占位成员。三、CHECK 不加 unmapped，值表外归 internal。四、dbt 作为增量 DAG 的第二个任务。</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>一、同一坐席在话单与参照数据里会算出两个键。二、占位成员会被当成真实维度成员统计，且 dim 的 NOT NULL 列只能编造。三、违反 DD-06，已知内部呼叫与未知码混在一起。四、耦合失败路径：dbt 失败重试期间接入停摆。</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>低至中（多为 dbt 模型与两个小结构变更；src_system 与 site_code 一旦有数据即不可逆）</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>DD-06 · DD-60 · DD-74 · DD-77 · DD-78 · DD-82 · DD-89 · LD-02 第 3、4、6、9 章 · LD-01 4.3 · if03a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DD-92</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>caller_number_hash 的算法定为 HMAC-SHA256（密钥只存 /etc/oss911，不入库），规范化后计算；本批先留空，密钥传入 dbt 的路径随 LD-07 那批设计</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>fact_call_leg.caller_number_hash 无算法、盐与规范化规则（DD-35 敏感字段）。不加盐的号码哈希可穷举还原；CALLERNO 可为邮件或网址。M-C15 以它为分组键。</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>一、算法 HMAC-SHA256，密钥由剧本生成、存 /etc/oss911（0600）、不入库、不入契约。二、规范化：数字串去掉非数字并去前导 00 / +，其余（邮件、网址）小写去首尾空白，前缀类型标记（n: / e: / u:）后再计算。三、core 保留 caller_number 明文列（受 DD-35 可见性矩阵约束），故哈希可随时按新密钥或新规则整体重算，历史不会断档——这是本步可以先留空的依据。四、dbt 取密钥的路径（不经 dbt 变量进入日志）在 LD-07 的实现批次定，定下即补算。</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>一、SHA-256 不加盐。二、现在随手定一个算法先写入。三、不存哈希，M-C15 直接按明文分组。</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>一、11 位号码空间可在普通硬件上穷举还原，等于没有保护。二、密钥传入路径没想清楚就实现，密钥会出现在 dbt 日志或 manifest 里。三、分组查询必须能读明文列，等于把 M-C15 的使用者全部提升到可见号码的角色。</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>低（留空列，后补；重算可行）</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>DD-35 · REQ-GOV-02 · M-C15 · LD-07 2.2 · LD-02 第 3 章</t>
         </is>
       </c>
     </row>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -5930,7 +5930,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>见 LD-02 第 3 章末补充段的十二条。要点：src_system 按系统不按源，使同一系统的坐席工号在维度与事实上算出同一键；归档单独为 cad_archive，以免割接并行期与 CAD 撞键；unmapped 是 DD-06「未映射不得归入其他」在 CHECK 上的落实；写入判定按 core 行派生内容而非源端原文，否则归类表更正与维度补齐永远写不进去；dbt 不接在增量 DAG 之后，因同一 DAG 内 max_active_runs = 1 会让 dbt 重试堵住接入。</t>
+          <t>见 LD-02 第 3 章末补充段的十二条。要点：src_system 按系统不按源，使同一系统的坐席工号在维度与事实上算出同一键；归档单独为 cad_archive，以免割接并行期与 CAD 撞键；unmapped 是 DD-06「未映射不得归入其他」在 CHECK 上的落实；写入判定按 core 行派生内容而非源端原文，否则归类表更正与维度补齐永远写不进去；dbt 不接在增量 DAG 之后，因同一 DAG 内 max_active_runs = 1 会让 dbt 重试堵住接入。 ——【2026-10-27 Gavin 定】dim_site 的 MKK 行：name_en = Makkah，name_ar = مكة المكرمة。</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -824,6 +824,13 @@
       <c r="A69" t="inlineStr">
         <is>
           <t>2026-10-27：新增 DD-91（core 装载规则十二处）、DD-92（caller_number_hash 算法，先留空）；LD-10 三条用例编号改为 TC-DISC-19/20/21（原编号与 test/cases_seed.csv 冲突）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-27：新增 DD-93（pgBouncer 池命名与 HBA 护栏）；DD-67 加注。</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4922,7 +4929,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>一、顺序定为 应用 → pgBouncer → HAProxy → 当前主库。pgBouncer 的后端固定为本机 HAProxy；HAProxy 以 Patroni 的 REST /primary 作健康检查选主。二、两个池：业务查询走事务级，Airflow / dbt / 人工运维走会话级；会话池大小即 dbt 并发上限，两数绑定。三、LB 对按 active/passive（VIP 浮动）部署。四、生产 max_connections 由 100 提至 200，为切换瞬间的池叠加与临时人工连接留出名额。</t>
+          <t>一、顺序定为 应用 → pgBouncer → HAProxy → 当前主库。pgBouncer 的后端固定为本机 HAProxy；HAProxy 以 Patroni 的 REST /primary 作健康检查选主。二、两个池：业务查询走事务级，Airflow / dbt / 人工运维走会话级；会话池大小即 dbt 并发上限，两数绑定。三、LB 对按 active/passive（VIP 浮动）部署。四、生产 max_connections 由 100 提至 200，为切换瞬间的池叠加与临时人工连接留出名额。 ——【2026-10-27 注】会话池别名 oss911_etl 与真实库名不同，dbt 的三段式名字被 PostgreSQL 拒绝；DD-93 把会话池改名为 oss911、事务池为 oss911_txn，并以 HBA 拒绝错配。本条「按库名选池模式」不变。</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5993,6 +6000,48 @@
       <c r="H93" t="inlineStr">
         <is>
           <t>DD-35 · REQ-GOV-02 · M-C15 · LD-07 2.2 · LD-02 第 3 章</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DD-93</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>pgBouncer 的会话池以真实库名 oss911 命名、事务池改名 oss911_txn；以 HBA 按「池 × 用户」拒绝错配；ingest 与 dbt 同用 oss911</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>dbt 真机首次构建失败：dbt-postgres 把每个关系渲染成「库名.schema.表」且校验库名等于 profile 的 dbname，而 profile 连的是 pgBouncer 会话池的别名 oss911_etl，PostgreSQL 见到与当前库 oss911 不同的库名即报「cross-database references are not implemented」。dbt 内无解（覆盖库名被 dbt 自身拒绝）。开发机临时库直连真实库名，未经别名，故未测出（2026-10-27）。</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>一、两个池互换名字：会话池 = oss911（与真实库名相同，dbt / ingest / 运维用），事务池 = oss911_txn（服务层用）。DD-67「按库名选池模式」不变，只改名。二、护栏：pgBouncer auth_type = hba，HBA 文件按池名与用户拒绝错配——query_svc / admin_svc 连 oss911 一律 reject，dbt 与 ingest 的登录用户连 oss911_txn 一律 reject；连错池立刻失败，不是偶发慢。三、ingest.conf 的库名随之改为 oss911。四、cad_mirror 池名本就等于库名，不受影响。</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>一、B：只留一个名字，池模式在 [users] 段按登录用户设。二、C：dbt 绕过 pgBouncer 直连 HAProxy。三、A 不加护栏。</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>一、池模式从「按库名」变为「按用户」，新增登录用户忘了设模式不报错、只偶发失败。二、违反 DD-67，dbt 连接数脱离全局上限。三、会话池占了最自然的名字，将来服务层顺手连 oss911 会把事务级查询压到会话池，连接数耗尽才发现。</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>低（改名与配置；pgBouncer 重启一次；HBA 文件随登录用户增减维护）</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>DD-67 · DD-74 · DD-83 · LD-08 第 3 章 · runbook 05 / 08 / 13</t>
         </is>
       </c>
     </row>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -6021,7 +6021,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>一、两个池互换名字：会话池 = oss911（与真实库名相同，dbt / ingest / 运维用），事务池 = oss911_txn（服务层用）。DD-67「按库名选池模式」不变，只改名。二、护栏：pgBouncer auth_type = hba，HBA 文件按池名与用户拒绝错配——query_svc / admin_svc 连 oss911 一律 reject，dbt 与 ingest 的登录用户连 oss911_txn 一律 reject；连错池立刻失败，不是偶发慢。三、ingest.conf 的库名随之改为 oss911。四、cad_mirror 池名本就等于库名，不受影响。</t>
+          <t>一、两个池互换名字：会话池 = oss911（与真实库名相同，dbt / ingest / 运维用），事务池 = oss911_txn（服务层用）。DD-67「按库名选池模式」不变，只改名。二、护栏：pgBouncer auth_type = hba，HBA 文件按池名与用户拒绝错配——query_svc / admin_svc 连 oss911 一律 reject，dbt 与 ingest 的登录用户连 oss911_txn 一律 reject；连错池立刻失败，不是偶发慢。三、ingest.conf 的库名随之改为 oss911。四、cad_mirror 池名本就等于库名，不受影响。 ——【2026-10-27 核查】别名 oss911_txn 的使用者只有服务层与 Superset。Superset（上游源码 db_engine_specs/postgres.py）：生成 SQL 不带 catalog（supports_cross_catalog_queries = False），无 dbt 式问题；但默认 catalog 取连接串库名（即别名）、catalog 列表查 pg_database（真实名）、切换 catalog 时改写连接串库名重连——受数据库 extra 的 allow_multi_catalog 控制，默认 false。要求：Superset 连接串库名 oss911_txn，allow_multi_catalog 保持 false；安装后按实际版本经 pgBouncer 实测 SQL Lab 与数据集预览。服务层代码纪律：SQL 不写三段式名。Airflow、Keycloak、cad_mirror 的池名即真实库名，不受影响。</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,13 @@
       <c r="A70" t="inlineStr">
         <is>
           <t>2026-10-27：新增 DD-93（pgBouncer 池命名与 HBA 护栏）；DD-67 加注。</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-27：新增 DD-94（if03d 参照数据装载规则十四处）；DD-56、DD-82 加注；ICP 问题单增补 Q33–Q35。</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4467,7 +4474,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>译名挂在自然键上（译的是实体，不是 SCD2 的某个版本），并记下确认当时源端的原文（meta.label_override.source_label_at_confirm，存原文而非哈希，以便 M-10 待办界面并排显示「确认时是这个、现在是这个」）。源端现值与之不符即置 pending_reconfirm，展现层回落显示源端原文而非可能已失效的旧译名，M-10 列出待办。不做任何名称规范化或格式差异过滤：客户答复改名频率为数年一次，为降误报引入规则表的成本超过其收益，且规则本身在交接时还要解释和维护。M-10 的全部参照数据维护（译名、班次窗口、朝觐期标识）逐字段写 audit.reference_data_change_log——参照数据不经 raw 层，没有 run_log 血缘，此表是唯一追溯来源。</t>
+          <t>译名挂在自然键上（译的是实体，不是 SCD2 的某个版本），并记下确认当时源端的原文（meta.label_override.source_label_at_confirm，存原文而非哈希，以便 M-10 待办界面并排显示「确认时是这个、现在是这个」）。源端现值与之不符即置 pending_reconfirm，展现层回落显示源端原文而非可能已失效的旧译名，M-10 列出待办。不做任何名称规范化或格式差异过滤：客户答复改名频率为数年一次，为降误报引入规则表的成本超过其收益，且规则本身在交接时还要解释和维护。M-10 的全部参照数据维护（译名、班次窗口、朝觐期标识）逐字段写 audit.reference_data_change_log——参照数据不经 raw 层，没有 run_log 血缘，此表是唯一追溯来源。 ——【2026-10-27 注】ICP 同步的技能队列只有一种名称：dim_queue 双语列先写原文，译名经 label_override 覆盖（DD-94 第八条）；源端改名即置 pending_reconfirm 由 dbt 写入。</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5559,7 +5566,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>一、raw：写入前查同一（幂等键，内容哈希）是否已存在于正常或已放行的批次中；已存在则不写，否则追加。已结束的话单通常只留一行，取到时尚在变化的留两行。二、去重判断不计待处理与已丢弃批次中的行，使被扣下的观测不挡后续观测（DD-76）。三、同一批次重试取到的内容相同，自然不重复写，不另设去重机制。四、core：按业务键只接受版本更大且内容哈希不同的观测；版本取源端给的版本标识（行级变更时间或数据集级版本号），源端都没有的（如 ICP 话单，结束后不再变化）取观测时间。数据集级版本号（如 ICP 参照数据的 config_version）按快照处理：更大则应用，快照中不再出现的实体置为非当前；相同则不动；更小则不应用、不静默丢弃，进待澄清队列并告警——版本倒退可能是平台回滚，也可能读到滞后节点，须由人判断。补数与归档迁入取到的旧快照因版本较小，不会盖掉较新的状态。五、时序倒置等坏数据写入 raw 并登记隔离。六、去重状态即 raw 本身，raw 表须有（幂等键，内容哈希）上的索引；接入角色须能读 meta.quarantine_batch。（同轮补充，2026-10-13：第四条由「源端变更时间」推广为「源端版本标识」，并写明数据集级版本号的快照规则——由开发机落实 if03d 时提出。）</t>
+          <t>一、raw：写入前查同一（幂等键，内容哈希）是否已存在于正常或已放行的批次中；已存在则不写，否则追加。已结束的话单通常只留一行，取到时尚在变化的留两行。二、去重判断不计待处理与已丢弃批次中的行，使被扣下的观测不挡后续观测（DD-76）。三、同一批次重试取到的内容相同，自然不重复写，不另设去重机制。四、core：按业务键只接受版本更大且内容哈希不同的观测；版本取源端给的版本标识（行级变更时间或数据集级版本号），源端都没有的（如 ICP 话单，结束后不再变化）取观测时间。数据集级版本号（如 ICP 参照数据的 config_version）按快照处理：更大则应用，快照中不再出现的实体置为非当前；相同则不动；更小则不应用、不静默丢弃，进待澄清队列并告警——版本倒退可能是平台回滚，也可能读到滞后节点，须由人判断。补数与归档迁入取到的旧快照因版本较小，不会盖掉较新的状态。五、时序倒置等坏数据写入 raw 并登记隔离。六、去重状态即 raw 本身，raw 表须有（幂等键，内容哈希）上的索引；接入角色须能读 meta.quarantine_batch。（同轮补充，2026-10-13：第四条由「源端变更时间」推广为「源端版本标识」，并写明数据集级版本号的快照规则——由开发机落实 if03d 时提出。） ——【2026-10-27 注】快照型参照数据（if03d）例外：版本变了整份快照写入（snapshot_on_version），同一版本重取不写；理由见 DD-94 第二条。</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6042,6 +6049,48 @@
       <c r="H94" t="inlineStr">
         <is>
           <t>DD-67 · DD-74 · DD-83 · LD-08 第 3 章 · runbook 05 / 08 / 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DD-94</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ICP 参照数据（if03d）装载规则十四处：经 raw 且整份快照、版本按 VDN、不调网关同步、SCD2 valid_from 取同步时刻且首版为哨兵、role_code 取 unmapped 待 M-10 维护、team_code 取坐席组、双语名先写原文、技能组多对多暂不落 dim、被叫配置不进 dim_channel、dbt 写维度与留痕</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>开发机逐页核对接口文档 synwas 一组（p.907–933、1029–1033）后发现契约 if03d 与文档多处不符（版本不按数据集、GET 读网关副本、roleId 是 CMS 权限角色、技能组多对多、被叫配置与 dim_channel 语义不同、双语名只有一个），加上 LD-01 9.3「参照数据不经 raw」与契约冲突，共十四处须定（2026-10-27 NOTES）。</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、role_code 写 unmapped；业务角色（接警员 / 调度员 / 主管）由 M-10 人工维护、SCD2 留痕，作为指定来源；Q35 仍问 ICP。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>一、参照数据不经 raw，接入程序直接写维度。二、raw 按数据集展开八张宽表。三、raw 只写变化的行（append_if_changed）。四、本方调用 synvdn 刷新网关副本。五、role_code 一律写 call_taker。六、技能与技能组现在就建桥表。</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>一、失去「当时收到的到底是什么」与重算能力，违反 DD-02 / DD-58。二、大半列为空且源端加字段就要改表，payload 原样已满足逐字一致。三、只写变化无法区分「没变」与「消失了」，而消失即置非当前是契约要求；数据量小，快照代价可忽略。四、写动作、会连带删除，不属只读接入。五、主管与调度员也有 ICP 工号，一律 call_taker 会把统计归错；DD-06 要求显式 unmapped。六、尚无指标需要按技能组汇总，先建即无依据的结构。</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>中（raw 表与权限为新增；SCD2 哨兵与 role_code 来源一旦有数据即难改）</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>DD-02 · DD-06 · DD-12 · DD-56 · DD-58 · DD-82 · DD-91 · AS-30 · LD-01 4.6 / 9.3 · LD-02 第 7、9 章 · if03d · ICP 问题单 Q33–Q35</t>
         </is>
       </c>
     </row>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -6060,7 +6060,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ICP 参照数据（if03d）装载规则十四处：经 raw 且整份快照、版本按 VDN、不调网关同步、SCD2 valid_from 取同步时刻且首版为哨兵、role_code 取 unmapped 待 M-10 维护、team_code 取坐席组、双语名先写原文、技能组多对多暂不落 dim、被叫配置不进 dim_channel、dbt 写维度与留痕</t>
+          <t>ICP 参照数据（if03d）装载规则十四处：经 raw 且整份快照、版本按 VDN、不调网关同步、SCD2 valid_from 取同步时刻且首版为哨兵、role_code 默认 call_taker、主管由 M-10 标记、team_code 取坐席组、双语名先写原文、技能组多对多暂不落 dim、被叫配置不进 dim_channel、dbt 写维度与留痕</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、role_code 写 unmapped；业务角色（接警员 / 调度员 / 主管）由 M-10 人工维护、SCD2 留痕，作为指定来源；Q35 仍问 ICP。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。</t>
+          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A71"/>
+  <dimension ref="A1:A72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -838,6 +838,13 @@
       <c r="A71" t="inlineStr">
         <is>
           <t>2026-10-27：新增 DD-94（if03d 参照数据装载规则十四处）；DD-56、DD-82 加注；ICP 问题单增补 Q33–Q35。</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-28：DD-94 原地补十五至十七（缺键快照整批隔离、角色标记带生效区间、staging 只处理配置的 VDN）。</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6077,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。</t>
+          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。 ——【2026-10-28 评审更正，原地改】十五、快照型数据集只要有一条缺自然键的记录即整批隔离（raw 照存），不得用不完整的快照做「消失即置非当前」的判断；全部缺键同样隔离。十六、M-10 的主管标记存为带生效区间的变更记录 meta.agent_role_override（agent_no、role_code、valid_from、valid_to、changed_by、reason），撤销是关 valid_to 不删行；dbt 按源端快照与 M-10 两类变化点的并集切 SCD2 版本，不同生效时刻的变化不合成一版（LD-02 第 7 章新增规则）。十七、staging 只处理契约配置的 VDN；其他 VDN 的快照留 raw 并进待澄清，不进维度模型；AS-30 被推翻时按其影响条款加 VDN 维，不现在把 vdn_id 塞进自然键。</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A72"/>
+  <dimension ref="A1:A73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -845,6 +845,13 @@
       <c r="A72" t="inlineStr">
         <is>
           <t>2026-10-28：DD-94 原地补十五至十七（缺键快照整批隔离、角色标记带生效区间、staging 只处理配置的 VDN）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-28：新增 DD-95（维度成员缺失的事实行归显式 unlinked 桶）；DD-94 补记开发机十四处并更正被拒方案五理由；DD-56 收窄。</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4481,7 +4488,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>译名挂在自然键上（译的是实体，不是 SCD2 的某个版本），并记下确认当时源端的原文（meta.label_override.source_label_at_confirm，存原文而非哈希，以便 M-10 待办界面并排显示「确认时是这个、现在是这个」）。源端现值与之不符即置 pending_reconfirm，展现层回落显示源端原文而非可能已失效的旧译名，M-10 列出待办。不做任何名称规范化或格式差异过滤：客户答复改名频率为数年一次，为降误报引入规则表的成本超过其收益，且规则本身在交接时还要解释和维护。M-10 的全部参照数据维护（译名、班次窗口、朝觐期标识）逐字段写 audit.reference_data_change_log——参照数据不经 raw 层，没有 run_log 血缘，此表是唯一追溯来源。 ——【2026-10-27 注】ICP 同步的技能队列只有一种名称：dim_queue 双语列先写原文，译名经 label_override 覆盖（DD-94 第八条）；源端改名即置 pending_reconfirm 由 dbt 写入。</t>
+          <t>译名挂在自然键上（译的是实体，不是 SCD2 的某个版本），并记下确认当时源端的原文（meta.label_override.source_label_at_confirm，存原文而非哈希，以便 M-10 待办界面并排显示「确认时是这个、现在是这个」）。源端现值与之不符即置 pending_reconfirm，展现层回落显示源端原文而非可能已失效的旧译名，M-10 列出待办。不做任何名称规范化或格式差异过滤：客户答复改名频率为数年一次，为降误报引入规则表的成本超过其收益，且规则本身在交接时还要解释和维护。M-10 的全部参照数据维护（译名、班次窗口、朝觐期标识）逐字段写 audit.reference_data_change_log——参照数据不经 raw 层，没有 run_log 血缘，此表是唯一追溯来源。 ——【2026-10-27 注】ICP 同步的技能队列只有一种名称：dim_queue 双语列先写原文，译名经 label_override 覆盖（DD-94 第八条）；源端改名即置 pending_reconfirm 由 dbt 写入。 ——【2026-10-28 注】「参照数据不经 raw、此表是唯一追溯来源」收窄为人工维护的参照数据；ICP 同步的变化由 dbt 写同一张留痕表（changed_by = icp_sync），经 raw（DD-94）。</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6077,7 +6084,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。 ——【2026-10-28 评审更正，原地改】十五、快照型数据集只要有一条缺自然键的记录即整批隔离（raw 照存），不得用不完整的快照做「消失即置非当前」的判断；全部缺键同样隔离。十六、M-10 的主管标记存为带生效区间的变更记录 meta.agent_role_override（agent_no、role_code、valid_from、valid_to、changed_by、reason），撤销是关 valid_to 不删行；dbt 按源端快照与 M-10 两类变化点的并集切 SCD2 版本，不同生效时刻的变化不合成一版（LD-02 第 7 章新增规则）。十七、staging 只处理契约配置的 VDN；其他 VDN 的快照留 raw 并进待澄清，不进维度模型；AS-30 被推翻时按其影响条款加 VDN 维，不现在把 vdn_id 塞进自然键。</t>
+          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。 ——【2026-10-28 评审更正，原地改】十五、快照型数据集只要有一条缺自然键的记录即整批隔离（raw 照存），不得用不完整的快照做「消失即置非当前」的判断；全部缺键同样隔离。十六、M-10 的主管标记存为带生效区间的变更记录 meta.agent_role_override（agent_no、role_code、valid_from、valid_to、changed_by、reason），撤销是关 valid_to 不删行；dbt 按源端快照与 M-10 两类变化点的并集切 SCD2 版本，不同生效时刻的变化不合成一版（LD-02 第 7 章新增规则）。十七、staging 只处理契约配置的 VDN；其他 VDN 的快照留 raw 并进待澄清，不进维度模型；AS-30 被推翻时按其影响条款加 VDN 维，不现在把 vdn_id 塞进自然键。 ——【2026-10-28 开发机实现中定的十四处，知悉并登记】已取版本记在 ingest_batch 的 snapshot_scope / snapshot_version / snapshot_synced_at，不写 watermark_state；隔离中的批次也算已取；首版哨兵 1970-01-01 UTC（-infinity 经 to_char 得 NULL）；副本过期只写 run_log message「STALE:」，监控批次接告警；reference_value 增 src_label、last_seen_at 改为最近变化时刻；每次构建只应用一份快照、从旧到新；已有话单由维度模型 post-hook 只对涉及的成员重新关联；dim_agent 名称两列同样先写原文；dbt 覆盖 get_columns_in_relation 跳过生成列；「版本变而内容无差异」为 warn 级 dbt 测试；transform 获 audit 的 USAGE；version_stale_days 可升可降。其中「缺键照写不隔离」「撤销即删行」「多 VDN 照常进维度」三处已被十五至十七推翻。</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6087,7 +6094,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>一、失去「当时收到的到底是什么」与重算能力，违反 DD-02 / DD-58。二、大半列为空且源端加字段就要改表，payload 原样已满足逐字一致。三、只写变化无法区分「没变」与「消失了」，而消失即置非当前是契约要求；数据量小，快照代价可忽略。四、写动作、会连带删除，不属只读接入。五、主管与调度员也有 ICP 工号，一律 call_taker 会把统计归错；DD-06 要求显式 unmapped。六、尚无指标需要按技能组汇总，先建即无依据的结构。</t>
+          <t>一、失去「当时收到的到底是什么」与重算能力，违反 DD-02 / DD-58。二、大半列为空且源端加字段就要改表，payload 原样已满足逐字一致。三、只写变化无法区分「没变」与「消失了」，而消失即置非当前是契约要求；数据量小，快照代价可忽略。四、写动作、会连带删除，不属只读接入。五、【2026-10-28 更正】写于得知 AS-36 之前：ICP 工号只有接警员与其主管，故一律 call_taker 基本正确，但主管仍须区分，由 M-10 标记（第六条更正）。六、尚无指标需要按技能组汇总，先建即无依据的结构。</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6098,6 +6105,48 @@
       <c r="H95" t="inlineStr">
         <is>
           <t>DD-02 · DD-06 · DD-12 · DD-56 · DD-58 · DD-82 · DD-91 · AS-30 · LD-01 4.6 / 9.3 · LD-02 第 7、9 章 · if03d · ICP 问题单 Q33–Q35</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DD-95</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>维度成员缺失的事实行：总量照计，分组指标归入显式「未关联」桶，不造哨兵成员、不拉长已关闭版本；每工号一条待澄清</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>真机实测：在假接口删除坐席 102 后，话单仍有 102 的坐席腿（51 条），通话开始时无有效维度版本，agent_sk 为空。现有一致性测试看不出（两边一致为空）。真实环境中会因配置删早、通话迟到、网关副本与话单节奏不一致而出现（2026-10-28 NOTES）。DD-06 只约束未映射码值，维度成员缺失无规则。</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>一、总量类指标照常计入。二、按坐席 / 队列分组的指标归入显式 unlinked 桶：有名字、报表可见、M-03 可下钻到原始工号；在 mart 按 sk 为空归入。三、不在维度表造「未知坐席」哨兵行；不把已关闭的版本拉长覆盖。四、每个工号开一条待澄清，未处理前不重复开；dbt 的 WARN 测试保留。五、成员重新出现属维度变化，post-hook 重新关联补上。</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>一、维度表造哨兵成员「未知坐席」。二、把已关闭的版本 valid_to 拉到无穷。三、从分组指标中剔除，只在总量里算。四、只保留 dbt WARN，不进待澄清。</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>一、哨兵成员会被当成真实成员参与统计与权限；且 DD-94 的维度由 dbt 按源重建，哨兵行要特殊对待。二、替源端断言成员仍存在，掩盖配置删早了这个事实。三、分组之和不等于总量，报表自相矛盾且无人能解释差额。四、WARN 只在构建输出里，没人日常看；根因需要人去问 ICP 运维。</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>低（mart 层归桶规则与一条待澄清写入）</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>DD-06 · DD-91 · DD-94 · LD-03 第 7 章 · REQ-RPT-06 · M-03</t>
         </is>
       </c>
     </row>

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A73"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -852,6 +852,13 @@
       <c r="A73" t="inlineStr">
         <is>
           <t>2026-10-28：新增 DD-95（维度成员缺失的事实行归显式 unlinked 桶）；DD-94 补记开发机十四处并更正被拒方案五理由；DD-56 收窄。</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-29：DD-94 补记开发机十一处（一处更正：角色标记版本的留痕 changed_by 取操作人）。</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6091,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。 ——【2026-10-28 评审更正，原地改】十五、快照型数据集只要有一条缺自然键的记录即整批隔离（raw 照存），不得用不完整的快照做「消失即置非当前」的判断；全部缺键同样隔离。十六、M-10 的主管标记存为带生效区间的变更记录 meta.agent_role_override（agent_no、role_code、valid_from、valid_to、changed_by、reason），撤销是关 valid_to 不删行；dbt 按源端快照与 M-10 两类变化点的并集切 SCD2 版本，不同生效时刻的变化不合成一版（LD-02 第 7 章新增规则）。十七、staging 只处理契约配置的 VDN；其他 VDN 的快照留 raw 并进待澄清，不进维度模型；AS-30 被推翻时按其影响条款加 VDN 维，不现在把 vdn_id 塞进自然键。 ——【2026-10-28 开发机实现中定的十四处，知悉并登记】已取版本记在 ingest_batch 的 snapshot_scope / snapshot_version / snapshot_synced_at，不写 watermark_state；隔离中的批次也算已取；首版哨兵 1970-01-01 UTC（-infinity 经 to_char 得 NULL）；副本过期只写 run_log message「STALE:」，监控批次接告警；reference_value 增 src_label、last_seen_at 改为最近变化时刻；每次构建只应用一份快照、从旧到新；已有话单由维度模型 post-hook 只对涉及的成员重新关联；dim_agent 名称两列同样先写原文；dbt 覆盖 get_columns_in_relation 跳过生成列；「版本变而内容无差异」为 warn 级 dbt 测试；transform 获 audit 的 USAGE；version_stale_days 可升可降。其中「缺键照写不隔离」「撤销即删行」「多 VDN 照常进维度」三处已被十五至十七推翻。</t>
+          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。 ——【2026-10-28 评审更正，原地改】十五、快照型数据集只要有一条缺自然键的记录即整批隔离（raw 照存），不得用不完整的快照做「消失即置非当前」的判断；全部缺键同样隔离。十六、M-10 的主管标记存为带生效区间的变更记录 meta.agent_role_override（agent_no、role_code、valid_from、valid_to、changed_by、reason），撤销是关 valid_to 不删行；dbt 按源端快照与 M-10 两类变化点的并集切 SCD2 版本，不同生效时刻的变化不合成一版（LD-02 第 7 章新增规则）。十七、staging 只处理契约配置的 VDN；其他 VDN 的快照留 raw 并进待澄清，不进维度模型；AS-30 被推翻时按其影响条款加 VDN 维，不现在把 vdn_id 塞进自然键。 ——【2026-10-28 开发机实现中定的十四处，知悉并登记】已取版本记在 ingest_batch 的 snapshot_scope / snapshot_version / snapshot_synced_at，不写 watermark_state；隔离中的批次也算已取；首版哨兵 1970-01-01 UTC（-infinity 经 to_char 得 NULL）；副本过期只写 run_log message「STALE:」，监控批次接告警；reference_value 增 src_label、last_seen_at 改为最近变化时刻；每次构建只应用一份快照、从旧到新；已有话单由维度模型 post-hook 只对涉及的成员重新关联；dim_agent 名称两列同样先写原文；dbt 覆盖 get_columns_in_relation 跳过生成列；「版本变而内容无差异」为 warn 级 dbt 测试；transform 获 audit 的 USAGE；version_stale_days 可升可降。其中「缺键照写不隔离」「撤销即删行」「多 VDN 照常进维度」三处已被十五至十七推翻。 ——【2026-10-29 开发机实现中定的十一处，知悉并登记】一次构建应用全部待应用快照（变化点并集所需）；补登过去的角色标记从该成员最新版本之后一秒生效、不改写已生效版本，M-10 录入时显示「将从 X 起生效」并要求确认、记录保留 requested_from；起点在将来的标记到点后才切版；agent_role_override 带 site_code / src_system / override_id / recorded_at，同一成员区间不重叠用排他约束（btree_gist 由 20-database 建，真机先 20 后 40）；M-10 只能 INSERT 与 UPDATE(valid_to)；标记引起的维度版本留痕 changed_by 取标记的操作人、reason「(role mark)」，icp_sync 只用于源端驱动的版本（更正开发机原定）；契约 v3 增 endpoint.site_vdn 必填，开发值随发布进生产，列入发布核对清单必核项；出现 site_vdn 以外的 VDN 或 site_vdn 不在版本号里各开待澄清；staging 不登记其他 VDN 的批次；DD-95 待澄清由 fact_call_leg 与两个维度模型的 post-hook 开、归 icp_reference；mart 的 unlinked 桶随 fact_call 一批实现。</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A74"/>
+  <dimension ref="A1:A75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -859,6 +859,13 @@
       <c r="A74" t="inlineStr">
         <is>
           <t>2026-10-29：DD-94 补记开发机十一处（一处更正：角色标记版本的留痕 changed_by 取操作人）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-29：DD-94 补记 requested_from / cleared_by 与按字段留痕。</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6098,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。 ——【2026-10-28 评审更正，原地改】十五、快照型数据集只要有一条缺自然键的记录即整批隔离（raw 照存），不得用不完整的快照做「消失即置非当前」的判断；全部缺键同样隔离。十六、M-10 的主管标记存为带生效区间的变更记录 meta.agent_role_override（agent_no、role_code、valid_from、valid_to、changed_by、reason），撤销是关 valid_to 不删行；dbt 按源端快照与 M-10 两类变化点的并集切 SCD2 版本，不同生效时刻的变化不合成一版（LD-02 第 7 章新增规则）。十七、staging 只处理契约配置的 VDN；其他 VDN 的快照留 raw 并进待澄清，不进维度模型；AS-30 被推翻时按其影响条款加 VDN 维，不现在把 vdn_id 塞进自然键。 ——【2026-10-28 开发机实现中定的十四处，知悉并登记】已取版本记在 ingest_batch 的 snapshot_scope / snapshot_version / snapshot_synced_at，不写 watermark_state；隔离中的批次也算已取；首版哨兵 1970-01-01 UTC（-infinity 经 to_char 得 NULL）；副本过期只写 run_log message「STALE:」，监控批次接告警；reference_value 增 src_label、last_seen_at 改为最近变化时刻；每次构建只应用一份快照、从旧到新；已有话单由维度模型 post-hook 只对涉及的成员重新关联；dim_agent 名称两列同样先写原文；dbt 覆盖 get_columns_in_relation 跳过生成列；「版本变而内容无差异」为 warn 级 dbt 测试；transform 获 audit 的 USAGE；version_stale_days 可升可降。其中「缺键照写不隔离」「撤销即删行」「多 VDN 照常进维度」三处已被十五至十七推翻。 ——【2026-10-29 开发机实现中定的十一处，知悉并登记】一次构建应用全部待应用快照（变化点并集所需）；补登过去的角色标记从该成员最新版本之后一秒生效、不改写已生效版本，M-10 录入时显示「将从 X 起生效」并要求确认、记录保留 requested_from；起点在将来的标记到点后才切版；agent_role_override 带 site_code / src_system / override_id / recorded_at，同一成员区间不重叠用排他约束（btree_gist 由 20-database 建，真机先 20 后 40）；M-10 只能 INSERT 与 UPDATE(valid_to)；标记引起的维度版本留痕 changed_by 取标记的操作人、reason「(role mark)」，icp_sync 只用于源端驱动的版本（更正开发机原定）；契约 v3 增 endpoint.site_vdn 必填，开发值随发布进生产，列入发布核对清单必核项；出现 site_vdn 以外的 VDN 或 site_vdn 不在版本号里各开待澄清；staging 不登记其他 VDN 的批次；DD-95 待澄清由 fact_call_leg 与两个维度模型的 post-hook 开、归 icp_reference；mart 的 unlinked 桶随 fact_call 一批实现。</t>
+          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。 ——【2026-10-28 评审更正，原地改】十五、快照型数据集只要有一条缺自然键的记录即整批隔离（raw 照存），不得用不完整的快照做「消失即置非当前」的判断；全部缺键同样隔离。十六、M-10 的主管标记存为带生效区间的变更记录 meta.agent_role_override（agent_no、role_code、valid_from、valid_to、changed_by、reason），撤销是关 valid_to 不删行；dbt 按源端快照与 M-10 两类变化点的并集切 SCD2 版本，不同生效时刻的变化不合成一版（LD-02 第 7 章新增规则）。十七、staging 只处理契约配置的 VDN；其他 VDN 的快照留 raw 并进待澄清，不进维度模型；AS-30 被推翻时按其影响条款加 VDN 维，不现在把 vdn_id 塞进自然键。 ——【2026-10-28 开发机实现中定的十四处，知悉并登记】已取版本记在 ingest_batch 的 snapshot_scope / snapshot_version / snapshot_synced_at，不写 watermark_state；隔离中的批次也算已取；首版哨兵 1970-01-01 UTC（-infinity 经 to_char 得 NULL）；副本过期只写 run_log message「STALE:」，监控批次接告警；reference_value 增 src_label、last_seen_at 改为最近变化时刻；每次构建只应用一份快照、从旧到新；已有话单由维度模型 post-hook 只对涉及的成员重新关联；dim_agent 名称两列同样先写原文；dbt 覆盖 get_columns_in_relation 跳过生成列；「版本变而内容无差异」为 warn 级 dbt 测试；transform 获 audit 的 USAGE；version_stale_days 可升可降。其中「缺键照写不隔离」「撤销即删行」「多 VDN 照常进维度」三处已被十五至十七推翻。 ——【2026-10-29 开发机实现中定的十一处，知悉并登记】一次构建应用全部待应用快照（变化点并集所需）；补登过去的角色标记从该成员最新版本之后一秒生效、不改写已生效版本，M-10 录入时显示「将从 X 起生效」并要求确认、记录保留 requested_from；起点在将来的标记到点后才切版；agent_role_override 带 site_code / src_system / override_id / recorded_at，同一成员区间不重叠用排他约束（btree_gist 由 20-database 建，真机先 20 后 40）；M-10 只能 INSERT 与 UPDATE(valid_to)；标记引起的维度版本留痕 changed_by 取标记的操作人、reason「(role mark)」，icp_sync 只用于源端驱动的版本（更正开发机原定）；契约 v3 增 endpoint.site_vdn 必填，开发值随发布进生产，列入发布核对清单必核项；出现 site_vdn 以外的 VDN 或 site_vdn 不在版本号里各开待澄清；staging 不登记其他 VDN 的批次；DD-95 待澄清由 fact_call_leg 与两个维度模型的 post-hook 开、归 icp_reference；mart 的 unlinked 桶随 fact_call 一批实现。 ——【2026-10-29 补记】agent_role_override 增 requested_from（M-10 确认后 valid_from 写实际生效点、原申请起点留存）与 cleared_by（撤销人，仅 valid_to 非无穷时可填，M-10 获 UPDATE(cleared_by)）；撤销引起的版本留痕取 coalesce(cleared_by, changed_by)；留痕按字段分：role_code 行记标记操作人，源端字段与 is_current 记 icp_sync。被拒：另建撤销记录表；撤销改为插入 call_taker 标记（与十六条冲突，且「回到默认」与「明确标为接警员」无法区分）。</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A75"/>
+  <dimension ref="A1:A76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -866,6 +866,13 @@
       <c r="A75" t="inlineStr">
         <is>
           <t>2026-10-29：DD-94 补记 requested_from / cleared_by 与按字段留痕。</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-30：DD-94 补十九（空快照基线取可信快照）、二十（构建 REPEATABLE READ、时间轴只算一次、M-10 写入协议）。</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6105,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。 ——【2026-10-28 评审更正，原地改】十五、快照型数据集只要有一条缺自然键的记录即整批隔离（raw 照存），不得用不完整的快照做「消失即置非当前」的判断；全部缺键同样隔离。十六、M-10 的主管标记存为带生效区间的变更记录 meta.agent_role_override（agent_no、role_code、valid_from、valid_to、changed_by、reason），撤销是关 valid_to 不删行；dbt 按源端快照与 M-10 两类变化点的并集切 SCD2 版本，不同生效时刻的变化不合成一版（LD-02 第 7 章新增规则）。十七、staging 只处理契约配置的 VDN；其他 VDN 的快照留 raw 并进待澄清，不进维度模型；AS-30 被推翻时按其影响条款加 VDN 维，不现在把 vdn_id 塞进自然键。 ——【2026-10-28 开发机实现中定的十四处，知悉并登记】已取版本记在 ingest_batch 的 snapshot_scope / snapshot_version / snapshot_synced_at，不写 watermark_state；隔离中的批次也算已取；首版哨兵 1970-01-01 UTC（-infinity 经 to_char 得 NULL）；副本过期只写 run_log message「STALE:」，监控批次接告警；reference_value 增 src_label、last_seen_at 改为最近变化时刻；每次构建只应用一份快照、从旧到新；已有话单由维度模型 post-hook 只对涉及的成员重新关联；dim_agent 名称两列同样先写原文；dbt 覆盖 get_columns_in_relation 跳过生成列；「版本变而内容无差异」为 warn 级 dbt 测试；transform 获 audit 的 USAGE；version_stale_days 可升可降。其中「缺键照写不隔离」「撤销即删行」「多 VDN 照常进维度」三处已被十五至十七推翻。 ——【2026-10-29 开发机实现中定的十一处，知悉并登记】一次构建应用全部待应用快照（变化点并集所需）；补登过去的角色标记从该成员最新版本之后一秒生效、不改写已生效版本，M-10 录入时显示「将从 X 起生效」并要求确认、记录保留 requested_from；起点在将来的标记到点后才切版；agent_role_override 带 site_code / src_system / override_id / recorded_at，同一成员区间不重叠用排他约束（btree_gist 由 20-database 建，真机先 20 后 40）；M-10 只能 INSERT 与 UPDATE(valid_to)；标记引起的维度版本留痕 changed_by 取标记的操作人、reason「(role mark)」，icp_sync 只用于源端驱动的版本（更正开发机原定）；契约 v3 增 endpoint.site_vdn 必填，开发值随发布进生产，列入发布核对清单必核项；出现 site_vdn 以外的 VDN 或 site_vdn 不在版本号里各开待澄清；staging 不登记其他 VDN 的批次；DD-95 待澄清由 fact_call_leg 与两个维度模型的 post-hook 开、归 icp_reference；mart 的 unlinked 桶随 fact_call 一批实现。 ——【2026-10-29 补记】agent_role_override 增 requested_from（M-10 确认后 valid_from 写实际生效点、原申请起点留存）与 cleared_by（撤销人，仅 valid_to 非无穷时可填，M-10 获 UPDATE(cleared_by)）；撤销引起的版本留痕取 coalesce(cleared_by, changed_by)；留痕按字段分：role_code 行记标记操作人，源端字段与 is_current 记 icp_sync。被拒：另建撤销记录表；撤销改为插入 call_taker 标记（与十六条冲突，且「回到默认」与「明确标为接警员」无法区分）。</t>
+          <t>一、经 raw（raw.icp_reference，通用列 + payload 原样）；LD-01 9.3 收窄为「M-10 人工维护的不经 raw」。二、版本变了整份快照写入，每数据集一批，core 以最新快照判消失；契约 raw_write.mode 改 snapshot_on_version。三、vdns 用 CTI 版本、其余用 VDN 版本，水位按 (ccId, vdnId)；只在 status = 2 取数。四、不调 syncti / synvdn；endTime 超 N 天（首版 7，热调 version_stale_days）未变告警；Q33 问网关是否自动同步。五、valid_from 取同步 endTime，首版取哨兵（早于一切事实；sk_scd 须能表示）。六、【2026-10-27 同日更正，Gavin 告知 ICP 的工号只有接警员与其主管、调度员不接电话（AS-36）】ICP 同步的坐席 role_code 默认 call_taker；主管由 M-10 标记为 supervisor（SCD2 留痕）；调度员的维度行将来自 CAD 上下岗记录，不经 ICP。Q35 仍问 ICP，不再阻塞。七、team_code 取 groupId，组名进 reference_value，monitorId 不落 core。八、dim_queue 双语列先写 skillName 原文，译名走 label_override。九、技能组多对多：skill_group_code 留空，成员关系只在 raw，需要时立桥表。十、calledconfigs 只落 raw，不进 dim_channel；落点待有指标需要时定。十一、oss911_transform 获 dim_agent / dim_queue 的 INSERT 与 UPDATE(valid_to, built_at)、reference_value 的 INSERT / UPDATE、reference_data_change_log 的 INSERT、label_override 的 UPDATE(state, flagged_at)。十二、版本更小由接入程序判、进待澄清；版本变而内容无差异由 dbt 判、记日志告警。十三、全部技能入 dim_queue，realFlag 只在 raw。十四、agentName 空或等于工号照写原文。 ——【2026-10-28 评审更正，原地改】十五、快照型数据集只要有一条缺自然键的记录即整批隔离（raw 照存），不得用不完整的快照做「消失即置非当前」的判断；全部缺键同样隔离。十六、M-10 的主管标记存为带生效区间的变更记录 meta.agent_role_override（agent_no、role_code、valid_from、valid_to、changed_by、reason），撤销是关 valid_to 不删行；dbt 按源端快照与 M-10 两类变化点的并集切 SCD2 版本，不同生效时刻的变化不合成一版（LD-02 第 7 章新增规则）。十七、staging 只处理契约配置的 VDN；其他 VDN 的快照留 raw 并进待澄清，不进维度模型；AS-30 被推翻时按其影响条款加 VDN 维，不现在把 vdn_id 塞进自然键。 ——【2026-10-28 开发机实现中定的十四处，知悉并登记】已取版本记在 ingest_batch 的 snapshot_scope / snapshot_version / snapshot_synced_at，不写 watermark_state；隔离中的批次也算已取；首版哨兵 1970-01-01 UTC（-infinity 经 to_char 得 NULL）；副本过期只写 run_log message「STALE:」，监控批次接告警；reference_value 增 src_label、last_seen_at 改为最近变化时刻；每次构建只应用一份快照、从旧到新；已有话单由维度模型 post-hook 只对涉及的成员重新关联；dim_agent 名称两列同样先写原文；dbt 覆盖 get_columns_in_relation 跳过生成列；「版本变而内容无差异」为 warn 级 dbt 测试；transform 获 audit 的 USAGE；version_stale_days 可升可降。其中「缺键照写不隔离」「撤销即删行」「多 VDN 照常进维度」三处已被十五至十七推翻。 ——【2026-10-29 开发机实现中定的十一处，知悉并登记】一次构建应用全部待应用快照（变化点并集所需）；补登过去的角色标记从该成员最新版本之后一秒生效、不改写已生效版本，M-10 录入时显示「将从 X 起生效」并要求确认、记录保留 requested_from；起点在将来的标记到点后才切版；agent_role_override 带 site_code / src_system / override_id / recorded_at，同一成员区间不重叠用排他约束（btree_gist 由 20-database 建，真机先 20 后 40）；M-10 只能 INSERT 与 UPDATE(valid_to)；标记引起的维度版本留痕 changed_by 取标记的操作人、reason「(role mark)」，icp_sync 只用于源端驱动的版本（更正开发机原定）；契约 v3 增 endpoint.site_vdn 必填，开发值随发布进生产，列入发布核对清单必核项；出现 site_vdn 以外的 VDN 或 site_vdn 不在版本号里各开待澄清；staging 不登记其他 VDN 的批次；DD-95 待澄清由 fact_call_leg 与两个维度模型的 post-hook 开、归 icp_reference；mart 的 unlinked 桶随 fact_call 一批实现。 ——【2026-10-29 补记】agent_role_override 增 requested_from（M-10 确认后 valid_from 写实际生效点、原申请起点留存）与 cleared_by（撤销人，仅 valid_to 非无穷时可填，M-10 获 UPDATE(cleared_by)）；撤销引起的版本留痕取 coalesce(cleared_by, changed_by)；留痕按字段分：role_code 行记标记操作人，源端字段与 is_current 记 icp_sync。被拒：另建撤销记录表；撤销改为插入 call_taker 标记（与十六条冲突，且「回到默认」与「明确标为接警员」无法区分）。 ——【2026-10-30 评审更正，原地改】十九、「取过哪个版本」算上隔离批次（防重抓），但「空快照能否接受」只与最近一份可信快照（未隔离、或已放行并应用）比较；连续空快照每一份都与同一基线比、每一份都隔离，异常不得成为新基线；确需清空全部配置走 M-03 显式放行。二十、维度构建在 REPEATABLE READ 下进行，且时间轴只计算一次落临时表，留痕、关旧版、插新版三步同读该表；M-10 写角色标记为独立短事务、不参加构建的咨询锁，构建期间提交的标记留到下一次构建应用。</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">

--- a/HD-04_约束与设计决策登记册.xlsx
+++ b/HD-04_约束与设计决策登记册.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A76"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -873,6 +873,13 @@
       <c r="A76" t="inlineStr">
         <is>
           <t>2026-10-30：DD-94 补十九（空快照基线取可信快照）、二十（构建 REPEATABLE READ、时间轴只算一次、M-10 写入协议）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-30：新增 DD-96（fact_call 聚合规则与 call_result 四值）、DD-97（注册表与 mart 的对应、版本后缀）。</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6171,6 +6178,90 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DD-96</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>fact_call 从腿级聚合的规则：首腿未到不建行、末腿未到标 is_complete=false 且发布指标只算完整通话、时间与归属取法、call_result 四值按「先看谁挂的再看有无坐席腿」判定；M-C06/07/11/15 四处口径修正</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>DD-66 定了通话级由腿级聚合、不独立接入，但 fact_call 每列怎么从腿算、呼叫结果怎么派生、首末腿缺失怎么办都没有规则；metrics.yaml 中 M-C07 定义与来源表矛盾、M-C11 用坐席腿的原因码而文档说只在末腿有意义（开发机 2026-10-26 列出的缺口）。</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>见 LD-03 2.4 的十条。要点：call_result 优先级 answered → abandoned（末腿主叫释放，不论在队列还是坐席振铃）→ unanswered_system → ivr_only，未完整为空；transferred / malicious 从结果码移为标志；M-C07 按坐席腿、M-C11 按通话取末腿改占比、M-C06 分母含放弃、M-C15 库内按号码分组只出计数。</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>一、坐席振铃中主叫挂断记 missed。二、未完整通话按现有腿判结果。三、M-C07 按通话平均。四、M-C11 按坐席腿。</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>一、放弃是主叫的行为，与电话当时在哪无关；坐席侧的未接由腿级 M-C12 计，混在结果码里会让一通电话同时「被放弃」又「被漏接」。二、进行中的通话会被判成放弃，第二天又变成应答，日内数字不稳。三、与定义「各腿分别计入」矛盾，且经多个坐席的通话会被低估。四、非末腿的原因码无意义（Q23），按腿统计是噪声。</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>中（结果码是报表分类的基础，dim_call_result 取值一旦有数据即难改；其余为模型规则）</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>DD-66 · DD-91 · DD-95 · LD-02 第 3 章 · LD-03 2.4 · M-C01–M-C15 · if03a</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DD-97</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>指标注册表不生成 SQL：mart 模型手写，metrics.yaml 以 mart_table / mart_column 指向实现，部署时校验一致；口径版本升级以带后缀的新列实现，旧列保留</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LD-03 第 5 章定了注册表是口径的权威、库内只读副本，但没定 mart 怎么由它产生、口径版本升级后历史怎么保留；第 8 步要开话务 mart。</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>一、不做 YAML 到 SQL 的生成器：mart 模型由人写 dbt，每条已发布指标在 metrics.yaml 中以 mart_table / mart_column 指向实现列，部署同步 meta.metric_registry 时校验列存在，否则失败。二、metric_version 升级：mart 新增带后缀的列（_v2），旧列保留，注册表按（编码, 版本）指向；历史报表不重算。三、参数型指标的参数记在注册表（M-C05 X 秒默认 20）。四、话务 mart 第一组四张表见 LD-03 第 5 章补充。</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>一、由 metrics.yaml 生成 mart SQL。二、口径升级就地改列、历史重算。</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>一、生成器要覆盖窗口、分母、过滤等全部语义，等于再造一个查询语言，八年维护成本大于收益；校验一致性已足以防止注册表与实现分叉。二、违反 LD-03 第 6 章与 DD-08「去年打印的报表今年重跑一致」。</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>低（约定与校验步骤；不改既有结构）</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>DD-05 · DD-08 · DD-49 · DD-81 · LD-03 第 5、6 章 · LD-04 第 7 章</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
